--- a/Nilai PTS dan ASAS Ganjil 2025-2026/Olah Nilai ASAS/X ASAS/X-2 ASAS INFORMATIKA (Jawaban).xlsx
+++ b/Nilai PTS dan ASAS Ganjil 2025-2026/Olah Nilai ASAS/X ASAS/X-2 ASAS INFORMATIKA (Jawaban).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21750" windowHeight="11950"/>
+    <workbookView windowWidth="14340" windowHeight="12360"/>
   </bookViews>
   <sheets>
     <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
@@ -691,7 +691,7 @@
     <numFmt numFmtId="178" formatCode="m/d/yyyy\ h:mm:ss"/>
     <numFmt numFmtId="179" formatCode="0&quot; / 30&quot;"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -705,6 +705,12 @@
       <name val="Arial"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1167,31 +1173,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1200,119 +1203,122 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1326,9 +1332,10 @@
     <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1381,11 +1388,11 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="37">
+  <dxfs count="62">
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1395,6 +1402,443 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -1747,93 +2191,6 @@
       </font>
     </dxf>
     <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF8F9FA"/>
@@ -1875,11 +2232,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle name="Form Responses 1-style" pivot="0" count="4" xr9:uid="{DEA9ECA7-5959-6CFE-4D82-2E6903BF83F9}">
-      <tableStyleElement type="wholeTable" dxfId="36"/>
-      <tableStyleElement type="headerRow" dxfId="35"/>
-      <tableStyleElement type="firstRowStripe" dxfId="34"/>
-      <tableStyleElement type="secondRowStripe" dxfId="33"/>
+    <tableStyle name="Form Responses 1-style" pivot="0" count="4" xr9:uid="{C66D167C-266C-FA4C-C9CF-4069903D515C}">
+      <tableStyleElement type="wholeTable" dxfId="61"/>
+      <tableStyleElement type="headerRow" dxfId="60"/>
+      <tableStyleElement type="firstRowStripe" dxfId="59"/>
+      <tableStyleElement type="secondRowStripe" dxfId="58"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2267,6 +2624,11 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
+        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{1e01fd6f-0bd6-4a26-891f-239252973749}"/>
+      </c:ext>
+    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2881,8 +3243,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Form_Responses" displayName="Form_Responses" ref="A1:BF47">
-  <sortState ref="A2:BF47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Form_Responses" displayName="Form_Responses" ref="A1:BF48">
+  <sortState ref="A1:BF48">
     <sortCondition ref="D2:D47"/>
   </sortState>
   <tableColumns count="58">
@@ -2921,31 +3283,31 @@
     <tableColumn id="33" name="Column1" dataDxfId="32">
       <calculatedColumnFormula>IF(H2=H$47,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="34" name="Column2"/>
-    <tableColumn id="35" name="Column3"/>
-    <tableColumn id="36" name="Column4"/>
-    <tableColumn id="37" name="Column5"/>
-    <tableColumn id="38" name="Column6"/>
-    <tableColumn id="39" name="Column7"/>
-    <tableColumn id="40" name="Column8"/>
-    <tableColumn id="41" name="Column9"/>
-    <tableColumn id="42" name="Column10"/>
-    <tableColumn id="43" name="Column11"/>
-    <tableColumn id="44" name="Column12"/>
-    <tableColumn id="45" name="Column13"/>
-    <tableColumn id="46" name="Column14"/>
-    <tableColumn id="47" name="Column15"/>
-    <tableColumn id="48" name="Column16"/>
-    <tableColumn id="49" name="Column17"/>
-    <tableColumn id="50" name="Column18"/>
-    <tableColumn id="51" name="Column19"/>
-    <tableColumn id="52" name="Column20"/>
-    <tableColumn id="53" name="Column21"/>
-    <tableColumn id="54" name="Column22"/>
-    <tableColumn id="55" name="Column23"/>
-    <tableColumn id="56" name="Column24"/>
-    <tableColumn id="57" name="Column25"/>
-    <tableColumn id="58" name="Column26"/>
+    <tableColumn id="34" name="Column2" dataDxfId="33"/>
+    <tableColumn id="35" name="Column3" dataDxfId="34"/>
+    <tableColumn id="36" name="Column4" dataDxfId="35"/>
+    <tableColumn id="37" name="Column5" dataDxfId="36"/>
+    <tableColumn id="38" name="Column6" dataDxfId="37"/>
+    <tableColumn id="39" name="Column7" dataDxfId="38"/>
+    <tableColumn id="40" name="Column8" dataDxfId="39"/>
+    <tableColumn id="41" name="Column9" dataDxfId="40"/>
+    <tableColumn id="42" name="Column10" dataDxfId="41"/>
+    <tableColumn id="43" name="Column11" dataDxfId="42"/>
+    <tableColumn id="44" name="Column12" dataDxfId="43"/>
+    <tableColumn id="45" name="Column13" dataDxfId="44"/>
+    <tableColumn id="46" name="Column14" dataDxfId="45"/>
+    <tableColumn id="47" name="Column15" dataDxfId="46"/>
+    <tableColumn id="48" name="Column16" dataDxfId="47"/>
+    <tableColumn id="49" name="Column17" dataDxfId="48"/>
+    <tableColumn id="50" name="Column18" dataDxfId="49"/>
+    <tableColumn id="51" name="Column19" dataDxfId="50"/>
+    <tableColumn id="52" name="Column20" dataDxfId="51"/>
+    <tableColumn id="53" name="Column21" dataDxfId="52"/>
+    <tableColumn id="54" name="Column22" dataDxfId="53"/>
+    <tableColumn id="55" name="Column23" dataDxfId="54"/>
+    <tableColumn id="56" name="Column24" dataDxfId="55"/>
+    <tableColumn id="57" name="Column25" dataDxfId="56"/>
+    <tableColumn id="58" name="Column26" dataDxfId="57"/>
   </tableColumns>
   <tableStyleInfo name="Form Responses 1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3449,103 +3811,103 @@
       <c r="AF2" s="3">
         <v>3</v>
       </c>
-      <c r="AG2" s="7">
+      <c r="AG2" s="5">
         <f>IF(H2=H$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AH2" s="7">
+      <c r="AH2" s="5">
         <f>IF(I2=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI2" s="7">
+      <c r="AI2" s="5">
         <f>IF(J2=J$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AJ2" s="7">
+      <c r="AJ2" s="5">
         <f>IF(K2=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK2" s="7">
+      <c r="AK2" s="5">
         <f>IF(L2=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL2" s="7">
+      <c r="AL2" s="5">
         <f>IF(M2=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM2" s="7">
+      <c r="AM2" s="5">
         <f>IF(N2=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN2" s="7">
+      <c r="AN2" s="5">
         <f>IF(O2=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO2" s="7">
+      <c r="AO2" s="5">
         <f>IF(P2=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP2" s="7">
+      <c r="AP2" s="5">
         <f>IF(Q2=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ2" s="7">
+      <c r="AQ2" s="5">
         <f>IF(R2=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR2" s="7">
+      <c r="AR2" s="5">
         <f>IF(S2=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS2" s="7">
+      <c r="AS2" s="5">
         <f>IF(T2=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT2" s="7">
+      <c r="AT2" s="5">
         <f>IF(U2=U$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AU2" s="7">
+      <c r="AU2" s="5">
         <f>IF(V2=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV2" s="7">
+      <c r="AV2" s="5">
         <f>IF(W2=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW2" s="7">
+      <c r="AW2" s="5">
         <f>IF(X2=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX2" s="7">
+      <c r="AX2" s="5">
         <f>IF(Y2=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY2" s="7">
+      <c r="AY2" s="5">
         <f>IF(Z2=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ2" s="7">
+      <c r="AZ2" s="5">
         <f>IF(AA2=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA2" s="7">
+      <c r="BA2" s="5">
         <f>IF(AB2=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB2" s="7">
+      <c r="BB2" s="5">
         <f>IF(AC2=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC2" s="7">
+      <c r="BC2" s="5">
         <f>IF(AD2=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD2" s="7">
+      <c r="BD2" s="5">
         <f>IF(AE2=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE2" s="7">
+      <c r="BE2" s="5">
         <f>IF(AF2=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -3651,103 +4013,103 @@
       <c r="AF3" s="3">
         <v>5</v>
       </c>
-      <c r="AG3" s="7">
+      <c r="AG3" s="5">
         <f>IF(H3=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH3" s="7">
+      <c r="AH3" s="5">
         <f>IF(I3=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI3" s="7">
+      <c r="AI3" s="5">
         <f>IF(J3=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ3" s="7">
+      <c r="AJ3" s="5">
         <f>IF(K3=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK3" s="7">
+      <c r="AK3" s="5">
         <f>IF(L3=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL3" s="7">
+      <c r="AL3" s="5">
         <f>IF(M3=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM3" s="7">
+      <c r="AM3" s="5">
         <f>IF(N3=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN3" s="7">
+      <c r="AN3" s="5">
         <f>IF(O3=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO3" s="7">
+      <c r="AO3" s="5">
         <f>IF(P3=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP3" s="7">
+      <c r="AP3" s="5">
         <f>IF(Q3=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ3" s="7">
+      <c r="AQ3" s="5">
         <f>IF(R3=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR3" s="7">
+      <c r="AR3" s="5">
         <f>IF(S3=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS3" s="7">
+      <c r="AS3" s="5">
         <f>IF(T3=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT3" s="7">
+      <c r="AT3" s="5">
         <f>IF(U3=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU3" s="7">
+      <c r="AU3" s="5">
         <f>IF(V3=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV3" s="7">
+      <c r="AV3" s="5">
         <f>IF(W3=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW3" s="7">
+      <c r="AW3" s="5">
         <f>IF(X3=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX3" s="7">
+      <c r="AX3" s="5">
         <f>IF(Y3=Y$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AY3" s="7">
+      <c r="AY3" s="5">
         <f>IF(Z3=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ3" s="7">
+      <c r="AZ3" s="5">
         <f>IF(AA3=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA3" s="7">
+      <c r="BA3" s="5">
         <f>IF(AB3=AB$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BB3" s="7">
+      <c r="BB3" s="5">
         <f>IF(AC3=AC$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BC3" s="7">
+      <c r="BC3" s="5">
         <f>IF(AD3=AD$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BD3" s="7">
+      <c r="BD3" s="5">
         <f>IF(AE3=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE3" s="7">
+      <c r="BE3" s="5">
         <f>IF(AF3=AF$47,1,0)</f>
         <v>0</v>
       </c>
@@ -3853,103 +4215,103 @@
       <c r="AF4" s="3">
         <v>3</v>
       </c>
-      <c r="AG4" s="7">
+      <c r="AG4" s="5">
         <f>IF(H4=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH4" s="7">
+      <c r="AH4" s="5">
         <f>IF(I4=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI4" s="7">
+      <c r="AI4" s="5">
         <f>IF(J4=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ4" s="7">
+      <c r="AJ4" s="5">
         <f>IF(K4=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK4" s="7">
+      <c r="AK4" s="5">
         <f>IF(L4=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL4" s="7">
+      <c r="AL4" s="5">
         <f>IF(M4=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM4" s="7">
+      <c r="AM4" s="5">
         <f>IF(N4=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN4" s="7">
+      <c r="AN4" s="5">
         <f>IF(O4=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO4" s="7">
+      <c r="AO4" s="5">
         <f>IF(P4=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP4" s="7">
+      <c r="AP4" s="5">
         <f>IF(Q4=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ4" s="7">
+      <c r="AQ4" s="5">
         <f>IF(R4=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR4" s="7">
+      <c r="AR4" s="5">
         <f>IF(S4=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS4" s="7">
+      <c r="AS4" s="5">
         <f>IF(T4=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT4" s="7">
+      <c r="AT4" s="5">
         <f>IF(U4=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU4" s="7">
+      <c r="AU4" s="5">
         <f>IF(V4=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV4" s="7">
+      <c r="AV4" s="5">
         <f>IF(W4=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW4" s="7">
+      <c r="AW4" s="5">
         <f>IF(X4=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX4" s="7">
+      <c r="AX4" s="5">
         <f>IF(Y4=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY4" s="7">
+      <c r="AY4" s="5">
         <f>IF(Z4=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ4" s="7">
+      <c r="AZ4" s="5">
         <f>IF(AA4=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA4" s="7">
+      <c r="BA4" s="5">
         <f>IF(AB4=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB4" s="7">
+      <c r="BB4" s="5">
         <f>IF(AC4=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC4" s="7">
+      <c r="BC4" s="5">
         <f>IF(AD4=AD$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BD4" s="7">
+      <c r="BD4" s="5">
         <f>IF(AE4=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE4" s="7">
+      <c r="BE4" s="5">
         <f>IF(AF4=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -4055,103 +4417,103 @@
       <c r="AF5" s="3">
         <v>3</v>
       </c>
-      <c r="AG5" s="7">
+      <c r="AG5" s="5">
         <f>IF(H5=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH5" s="7">
+      <c r="AH5" s="5">
         <f>IF(I5=I$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AI5" s="7">
+      <c r="AI5" s="5">
         <f>IF(J5=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ5" s="7">
+      <c r="AJ5" s="5">
         <f>IF(K5=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK5" s="7">
+      <c r="AK5" s="5">
         <f>IF(L5=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL5" s="7">
+      <c r="AL5" s="5">
         <f>IF(M5=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM5" s="7">
+      <c r="AM5" s="5">
         <f>IF(N5=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN5" s="7">
+      <c r="AN5" s="5">
         <f>IF(O5=O$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO5" s="7">
+      <c r="AO5" s="5">
         <f>IF(P5=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP5" s="7">
+      <c r="AP5" s="5">
         <f>IF(Q5=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ5" s="7">
+      <c r="AQ5" s="5">
         <f>IF(R5=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR5" s="7">
+      <c r="AR5" s="5">
         <f>IF(S5=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS5" s="7">
+      <c r="AS5" s="5">
         <f>IF(T5=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT5" s="7">
+      <c r="AT5" s="5">
         <f>IF(U5=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU5" s="7">
+      <c r="AU5" s="5">
         <f>IF(V5=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV5" s="7">
+      <c r="AV5" s="5">
         <f>IF(W5=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW5" s="7">
+      <c r="AW5" s="5">
         <f>IF(X5=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX5" s="7">
+      <c r="AX5" s="5">
         <f>IF(Y5=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY5" s="7">
+      <c r="AY5" s="5">
         <f>IF(Z5=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ5" s="7">
+      <c r="AZ5" s="5">
         <f>IF(AA5=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA5" s="7">
+      <c r="BA5" s="5">
         <f>IF(AB5=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB5" s="7">
+      <c r="BB5" s="5">
         <f>IF(AC5=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC5" s="7">
+      <c r="BC5" s="5">
         <f>IF(AD5=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD5" s="7">
+      <c r="BD5" s="5">
         <f>IF(AE5=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE5" s="7">
+      <c r="BE5" s="5">
         <f>IF(AF5=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -4257,103 +4619,103 @@
       <c r="AF6" s="3">
         <v>14</v>
       </c>
-      <c r="AG6" s="7">
+      <c r="AG6" s="5">
         <f>IF(H6=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH6" s="7">
+      <c r="AH6" s="5">
         <f>IF(I6=I$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AI6" s="7">
+      <c r="AI6" s="5">
         <f>IF(J6=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ6" s="7">
+      <c r="AJ6" s="5">
         <f>IF(K6=K$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AK6" s="7">
+      <c r="AK6" s="5">
         <f>IF(L6=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL6" s="7">
+      <c r="AL6" s="5">
         <f>IF(M6=M$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AM6" s="7">
+      <c r="AM6" s="5">
         <f>IF(N6=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN6" s="7">
+      <c r="AN6" s="5">
         <f>IF(O6=O$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO6" s="7">
+      <c r="AO6" s="5">
         <f>IF(P6=P$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AP6" s="7">
+      <c r="AP6" s="5">
         <f>IF(Q6=Q$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AQ6" s="7">
+      <c r="AQ6" s="5">
         <f>IF(R6=R$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AR6" s="7">
+      <c r="AR6" s="5">
         <f>IF(S6=S$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS6" s="7">
+      <c r="AS6" s="5">
         <f>IF(T6=T$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AT6" s="7">
+      <c r="AT6" s="5">
         <f>IF(U6=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU6" s="7">
+      <c r="AU6" s="5">
         <f>IF(V6=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV6" s="7">
+      <c r="AV6" s="5">
         <f>IF(W6=W$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AW6" s="7">
+      <c r="AW6" s="5">
         <f>IF(X6=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX6" s="7">
+      <c r="AX6" s="5">
         <f>IF(Y6=Y$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AY6" s="7">
+      <c r="AY6" s="5">
         <f>IF(Z6=Z$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AZ6" s="7">
+      <c r="AZ6" s="5">
         <f>IF(AA6=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA6" s="7">
+      <c r="BA6" s="5">
         <f>IF(AB6=AB$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BB6" s="7">
+      <c r="BB6" s="5">
         <f>IF(AC6=AC$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BC6" s="7">
+      <c r="BC6" s="5">
         <f>IF(AD6=AD$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BD6" s="7">
+      <c r="BD6" s="5">
         <f>IF(AE6=AE$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BE6" s="7">
+      <c r="BE6" s="5">
         <f>IF(AF6=AF$47,1,0)</f>
         <v>0</v>
       </c>
@@ -4459,103 +4821,103 @@
       <c r="AF7" s="3">
         <v>11</v>
       </c>
-      <c r="AG7" s="7">
+      <c r="AG7" s="5">
         <f>IF(H7=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH7" s="7">
+      <c r="AH7" s="5">
         <f>IF(I7=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI7" s="7">
+      <c r="AI7" s="5">
         <f>IF(J7=J$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AJ7" s="7">
+      <c r="AJ7" s="5">
         <f>IF(K7=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK7" s="7">
+      <c r="AK7" s="5">
         <f>IF(L7=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL7" s="7">
+      <c r="AL7" s="5">
         <f>IF(M7=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM7" s="7">
+      <c r="AM7" s="5">
         <f>IF(N7=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN7" s="7">
+      <c r="AN7" s="5">
         <f>IF(O7=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO7" s="7">
+      <c r="AO7" s="5">
         <f>IF(P7=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP7" s="7">
+      <c r="AP7" s="5">
         <f>IF(Q7=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ7" s="7">
+      <c r="AQ7" s="5">
         <f>IF(R7=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR7" s="7">
+      <c r="AR7" s="5">
         <f>IF(S7=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS7" s="7">
+      <c r="AS7" s="5">
         <f>IF(T7=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT7" s="7">
+      <c r="AT7" s="5">
         <f>IF(U7=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU7" s="7">
+      <c r="AU7" s="5">
         <f>IF(V7=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV7" s="7">
+      <c r="AV7" s="5">
         <f>IF(W7=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW7" s="7">
+      <c r="AW7" s="5">
         <f>IF(X7=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX7" s="7">
+      <c r="AX7" s="5">
         <f>IF(Y7=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY7" s="7">
+      <c r="AY7" s="5">
         <f>IF(Z7=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ7" s="7">
+      <c r="AZ7" s="5">
         <f>IF(AA7=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA7" s="7">
+      <c r="BA7" s="5">
         <f>IF(AB7=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB7" s="7">
+      <c r="BB7" s="5">
         <f>IF(AC7=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC7" s="7">
+      <c r="BC7" s="5">
         <f>IF(AD7=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD7" s="7">
+      <c r="BD7" s="5">
         <f>IF(AE7=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE7" s="7">
+      <c r="BE7" s="5">
         <f>IF(AF7=AF$47,1,0)</f>
         <v>0</v>
       </c>
@@ -4661,103 +5023,103 @@
       <c r="AF8" s="3">
         <v>3</v>
       </c>
-      <c r="AG8" s="7">
+      <c r="AG8" s="5">
         <f>IF(H8=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH8" s="7">
+      <c r="AH8" s="5">
         <f>IF(I8=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI8" s="7">
+      <c r="AI8" s="5">
         <f>IF(J8=J$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AJ8" s="7">
+      <c r="AJ8" s="5">
         <f>IF(K8=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK8" s="7">
+      <c r="AK8" s="5">
         <f>IF(L8=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL8" s="7">
+      <c r="AL8" s="5">
         <f>IF(M8=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM8" s="7">
+      <c r="AM8" s="5">
         <f>IF(N8=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN8" s="7">
+      <c r="AN8" s="5">
         <f>IF(O8=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO8" s="7">
+      <c r="AO8" s="5">
         <f>IF(P8=P$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AP8" s="7">
+      <c r="AP8" s="5">
         <f>IF(Q8=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ8" s="7">
+      <c r="AQ8" s="5">
         <f>IF(R8=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR8" s="7">
+      <c r="AR8" s="5">
         <f>IF(S8=S$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS8" s="7">
+      <c r="AS8" s="5">
         <f>IF(T8=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT8" s="7">
+      <c r="AT8" s="5">
         <f>IF(U8=U$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AU8" s="7">
+      <c r="AU8" s="5">
         <f>IF(V8=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV8" s="7">
+      <c r="AV8" s="5">
         <f>IF(W8=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW8" s="7">
+      <c r="AW8" s="5">
         <f>IF(X8=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX8" s="7">
+      <c r="AX8" s="5">
         <f>IF(Y8=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY8" s="7">
+      <c r="AY8" s="5">
         <f>IF(Z8=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ8" s="7">
+      <c r="AZ8" s="5">
         <f>IF(AA8=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA8" s="7">
+      <c r="BA8" s="5">
         <f>IF(AB8=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB8" s="7">
+      <c r="BB8" s="5">
         <f>IF(AC8=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC8" s="7">
+      <c r="BC8" s="5">
         <f>IF(AD8=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD8" s="7">
+      <c r="BD8" s="5">
         <f>IF(AE8=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE8" s="7">
+      <c r="BE8" s="5">
         <f>IF(AF8=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -4863,103 +5225,103 @@
       <c r="AF9" s="3">
         <v>3</v>
       </c>
-      <c r="AG9" s="7">
+      <c r="AG9" s="5">
         <f>IF(H9=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH9" s="7">
+      <c r="AH9" s="5">
         <f>IF(I9=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI9" s="7">
+      <c r="AI9" s="5">
         <f>IF(J9=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ9" s="7">
+      <c r="AJ9" s="5">
         <f>IF(K9=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK9" s="7">
+      <c r="AK9" s="5">
         <f>IF(L9=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL9" s="7">
+      <c r="AL9" s="5">
         <f>IF(M9=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM9" s="7">
+      <c r="AM9" s="5">
         <f>IF(N9=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN9" s="7">
+      <c r="AN9" s="5">
         <f>IF(O9=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO9" s="7">
+      <c r="AO9" s="5">
         <f>IF(P9=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP9" s="7">
+      <c r="AP9" s="5">
         <f>IF(Q9=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ9" s="7">
+      <c r="AQ9" s="5">
         <f>IF(R9=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR9" s="7">
+      <c r="AR9" s="5">
         <f>IF(S9=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS9" s="7">
+      <c r="AS9" s="5">
         <f>IF(T9=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT9" s="7">
+      <c r="AT9" s="5">
         <f>IF(U9=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU9" s="7">
+      <c r="AU9" s="5">
         <f>IF(V9=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV9" s="7">
+      <c r="AV9" s="5">
         <f>IF(W9=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW9" s="7">
+      <c r="AW9" s="5">
         <f>IF(X9=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX9" s="7">
+      <c r="AX9" s="5">
         <f>IF(Y9=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY9" s="7">
+      <c r="AY9" s="5">
         <f>IF(Z9=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ9" s="7">
+      <c r="AZ9" s="5">
         <f>IF(AA9=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA9" s="7">
+      <c r="BA9" s="5">
         <f>IF(AB9=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB9" s="7">
+      <c r="BB9" s="5">
         <f>IF(AC9=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC9" s="7">
+      <c r="BC9" s="5">
         <f>IF(AD9=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD9" s="7">
+      <c r="BD9" s="5">
         <f>IF(AE9=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE9" s="7">
+      <c r="BE9" s="5">
         <f>IF(AF9=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -5065,103 +5427,103 @@
       <c r="AF10" s="3">
         <v>3</v>
       </c>
-      <c r="AG10" s="7">
+      <c r="AG10" s="5">
         <f>IF(H10=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH10" s="7">
+      <c r="AH10" s="5">
         <f>IF(I10=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI10" s="7">
+      <c r="AI10" s="5">
         <f>IF(J10=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ10" s="7">
+      <c r="AJ10" s="5">
         <f>IF(K10=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK10" s="7">
+      <c r="AK10" s="5">
         <f>IF(L10=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL10" s="7">
+      <c r="AL10" s="5">
         <f>IF(M10=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM10" s="7">
+      <c r="AM10" s="5">
         <f>IF(N10=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN10" s="7">
+      <c r="AN10" s="5">
         <f>IF(O10=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO10" s="7">
+      <c r="AO10" s="5">
         <f>IF(P10=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP10" s="7">
+      <c r="AP10" s="5">
         <f>IF(Q10=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ10" s="7">
+      <c r="AQ10" s="5">
         <f>IF(R10=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR10" s="7">
+      <c r="AR10" s="5">
         <f>IF(S10=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS10" s="7">
+      <c r="AS10" s="5">
         <f>IF(T10=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT10" s="7">
+      <c r="AT10" s="5">
         <f>IF(U10=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU10" s="7">
+      <c r="AU10" s="5">
         <f>IF(V10=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV10" s="7">
+      <c r="AV10" s="5">
         <f>IF(W10=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW10" s="7">
+      <c r="AW10" s="5">
         <f>IF(X10=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX10" s="7">
+      <c r="AX10" s="5">
         <f>IF(Y10=Y$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AY10" s="7">
+      <c r="AY10" s="5">
         <f>IF(Z10=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ10" s="7">
+      <c r="AZ10" s="5">
         <f>IF(AA10=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA10" s="7">
+      <c r="BA10" s="5">
         <f>IF(AB10=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB10" s="7">
+      <c r="BB10" s="5">
         <f>IF(AC10=AC$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BC10" s="7">
+      <c r="BC10" s="5">
         <f>IF(AD10=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD10" s="7">
+      <c r="BD10" s="5">
         <f>IF(AE10=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE10" s="7">
+      <c r="BE10" s="5">
         <f>IF(AF10=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -5267,103 +5629,103 @@
       <c r="AF11" s="3">
         <v>3</v>
       </c>
-      <c r="AG11" s="7">
+      <c r="AG11" s="5">
         <f>IF(H11=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH11" s="7">
+      <c r="AH11" s="5">
         <f>IF(I11=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI11" s="7">
+      <c r="AI11" s="5">
         <f>IF(J11=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ11" s="7">
+      <c r="AJ11" s="5">
         <f>IF(K11=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK11" s="7">
+      <c r="AK11" s="5">
         <f>IF(L11=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL11" s="7">
+      <c r="AL11" s="5">
         <f>IF(M11=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM11" s="7">
+      <c r="AM11" s="5">
         <f>IF(N11=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN11" s="7">
+      <c r="AN11" s="5">
         <f>IF(O11=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO11" s="7">
+      <c r="AO11" s="5">
         <f>IF(P11=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP11" s="7">
+      <c r="AP11" s="5">
         <f>IF(Q11=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ11" s="7">
+      <c r="AQ11" s="5">
         <f>IF(R11=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR11" s="7">
+      <c r="AR11" s="5">
         <f>IF(S11=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS11" s="7">
+      <c r="AS11" s="5">
         <f>IF(T11=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT11" s="7">
+      <c r="AT11" s="5">
         <f>IF(U11=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU11" s="7">
+      <c r="AU11" s="5">
         <f>IF(V11=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV11" s="7">
+      <c r="AV11" s="5">
         <f>IF(W11=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW11" s="7">
+      <c r="AW11" s="5">
         <f>IF(X11=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX11" s="7">
+      <c r="AX11" s="5">
         <f>IF(Y11=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY11" s="7">
+      <c r="AY11" s="5">
         <f>IF(Z11=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ11" s="7">
+      <c r="AZ11" s="5">
         <f>IF(AA11=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA11" s="7">
+      <c r="BA11" s="5">
         <f>IF(AB11=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB11" s="7">
+      <c r="BB11" s="5">
         <f>IF(AC11=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC11" s="7">
+      <c r="BC11" s="5">
         <f>IF(AD11=AD$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BD11" s="7">
+      <c r="BD11" s="5">
         <f>IF(AE11=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE11" s="7">
+      <c r="BE11" s="5">
         <f>IF(AF11=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -5469,103 +5831,103 @@
       <c r="AF12" s="3">
         <v>3</v>
       </c>
-      <c r="AG12" s="7">
+      <c r="AG12" s="5">
         <f>IF(H12=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH12" s="7">
+      <c r="AH12" s="5">
         <f>IF(I12=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI12" s="7">
+      <c r="AI12" s="5">
         <f>IF(J12=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ12" s="7">
+      <c r="AJ12" s="5">
         <f>IF(K12=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK12" s="7">
+      <c r="AK12" s="5">
         <f>IF(L12=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL12" s="7">
+      <c r="AL12" s="5">
         <f>IF(M12=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM12" s="7">
+      <c r="AM12" s="5">
         <f>IF(N12=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN12" s="7">
+      <c r="AN12" s="5">
         <f>IF(O12=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO12" s="7">
+      <c r="AO12" s="5">
         <f>IF(P12=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP12" s="7">
+      <c r="AP12" s="5">
         <f>IF(Q12=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ12" s="7">
+      <c r="AQ12" s="5">
         <f>IF(R12=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR12" s="7">
+      <c r="AR12" s="5">
         <f>IF(S12=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS12" s="7">
+      <c r="AS12" s="5">
         <f>IF(T12=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT12" s="7">
+      <c r="AT12" s="5">
         <f>IF(U12=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU12" s="7">
+      <c r="AU12" s="5">
         <f>IF(V12=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV12" s="7">
+      <c r="AV12" s="5">
         <f>IF(W12=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW12" s="7">
+      <c r="AW12" s="5">
         <f>IF(X12=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX12" s="7">
+      <c r="AX12" s="5">
         <f>IF(Y12=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY12" s="7">
+      <c r="AY12" s="5">
         <f>IF(Z12=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ12" s="7">
+      <c r="AZ12" s="5">
         <f>IF(AA12=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA12" s="7">
+      <c r="BA12" s="5">
         <f>IF(AB12=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB12" s="7">
+      <c r="BB12" s="5">
         <f>IF(AC12=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC12" s="7">
+      <c r="BC12" s="5">
         <f>IF(AD12=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD12" s="7">
+      <c r="BD12" s="5">
         <f>IF(AE12=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE12" s="7">
+      <c r="BE12" s="5">
         <f>IF(AF12=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -5671,103 +6033,103 @@
       <c r="AF13" s="3">
         <v>12</v>
       </c>
-      <c r="AG13" s="7">
+      <c r="AG13" s="5">
         <f>IF(H13=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH13" s="7">
+      <c r="AH13" s="5">
         <f>IF(I13=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI13" s="7">
+      <c r="AI13" s="5">
         <f>IF(J13=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ13" s="7">
+      <c r="AJ13" s="5">
         <f>IF(K13=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK13" s="7">
+      <c r="AK13" s="5">
         <f>IF(L13=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL13" s="7">
+      <c r="AL13" s="5">
         <f>IF(M13=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM13" s="7">
+      <c r="AM13" s="5">
         <f>IF(N13=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN13" s="7">
+      <c r="AN13" s="5">
         <f>IF(O13=O$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO13" s="7">
+      <c r="AO13" s="5">
         <f>IF(P13=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP13" s="7">
+      <c r="AP13" s="5">
         <f>IF(Q13=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ13" s="7">
+      <c r="AQ13" s="5">
         <f>IF(R13=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR13" s="7">
+      <c r="AR13" s="5">
         <f>IF(S13=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS13" s="7">
+      <c r="AS13" s="5">
         <f>IF(T13=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT13" s="7">
+      <c r="AT13" s="5">
         <f>IF(U13=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU13" s="7">
+      <c r="AU13" s="5">
         <f>IF(V13=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV13" s="7">
+      <c r="AV13" s="5">
         <f>IF(W13=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW13" s="7">
+      <c r="AW13" s="5">
         <f>IF(X13=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX13" s="7">
+      <c r="AX13" s="5">
         <f>IF(Y13=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY13" s="7">
+      <c r="AY13" s="5">
         <f>IF(Z13=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ13" s="7">
+      <c r="AZ13" s="5">
         <f>IF(AA13=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA13" s="7">
+      <c r="BA13" s="5">
         <f>IF(AB13=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB13" s="7">
+      <c r="BB13" s="5">
         <f>IF(AC13=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC13" s="7">
+      <c r="BC13" s="5">
         <f>IF(AD13=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD13" s="7">
+      <c r="BD13" s="5">
         <f>IF(AE13=AE$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BE13" s="7">
+      <c r="BE13" s="5">
         <f>IF(AF13=AF$47,1,0)</f>
         <v>0</v>
       </c>
@@ -5873,103 +6235,103 @@
       <c r="AF14" s="3">
         <v>3</v>
       </c>
-      <c r="AG14" s="7">
+      <c r="AG14" s="5">
         <f>IF(H14=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH14" s="7">
+      <c r="AH14" s="5">
         <f>IF(I14=I$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AI14" s="7">
+      <c r="AI14" s="5">
         <f>IF(J14=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ14" s="7">
+      <c r="AJ14" s="5">
         <f>IF(K14=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK14" s="7">
+      <c r="AK14" s="5">
         <f>IF(L14=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL14" s="7">
+      <c r="AL14" s="5">
         <f>IF(M14=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM14" s="7">
+      <c r="AM14" s="5">
         <f>IF(N14=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN14" s="7">
+      <c r="AN14" s="5">
         <f>IF(O14=O$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO14" s="7">
+      <c r="AO14" s="5">
         <f>IF(P14=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP14" s="7">
+      <c r="AP14" s="5">
         <f>IF(Q14=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ14" s="7">
+      <c r="AQ14" s="5">
         <f>IF(R14=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR14" s="7">
+      <c r="AR14" s="5">
         <f>IF(S14=S$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS14" s="7">
+      <c r="AS14" s="5">
         <f>IF(T14=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT14" s="7">
+      <c r="AT14" s="5">
         <f>IF(U14=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU14" s="7">
+      <c r="AU14" s="5">
         <f>IF(V14=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV14" s="7">
+      <c r="AV14" s="5">
         <f>IF(W14=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW14" s="7">
+      <c r="AW14" s="5">
         <f>IF(X14=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX14" s="7">
+      <c r="AX14" s="5">
         <f>IF(Y14=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY14" s="7">
+      <c r="AY14" s="5">
         <f>IF(Z14=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ14" s="7">
+      <c r="AZ14" s="5">
         <f>IF(AA14=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA14" s="7">
+      <c r="BA14" s="5">
         <f>IF(AB14=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB14" s="7">
+      <c r="BB14" s="5">
         <f>IF(AC14=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC14" s="7">
+      <c r="BC14" s="5">
         <f>IF(AD14=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD14" s="7">
+      <c r="BD14" s="5">
         <f>IF(AE14=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE14" s="7">
+      <c r="BE14" s="5">
         <f>IF(AF14=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -6075,103 +6437,103 @@
       <c r="AF15" s="3">
         <v>3</v>
       </c>
-      <c r="AG15" s="7">
+      <c r="AG15" s="5">
         <f>IF(H15=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH15" s="7">
+      <c r="AH15" s="5">
         <f>IF(I15=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI15" s="7">
+      <c r="AI15" s="5">
         <f>IF(J15=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ15" s="7">
+      <c r="AJ15" s="5">
         <f>IF(K15=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK15" s="7">
+      <c r="AK15" s="5">
         <f>IF(L15=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL15" s="7">
+      <c r="AL15" s="5">
         <f>IF(M15=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM15" s="7">
+      <c r="AM15" s="5">
         <f>IF(N15=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN15" s="7">
+      <c r="AN15" s="5">
         <f>IF(O15=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO15" s="7">
+      <c r="AO15" s="5">
         <f>IF(P15=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP15" s="7">
+      <c r="AP15" s="5">
         <f>IF(Q15=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ15" s="7">
+      <c r="AQ15" s="5">
         <f>IF(R15=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR15" s="7">
+      <c r="AR15" s="5">
         <f>IF(S15=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS15" s="7">
+      <c r="AS15" s="5">
         <f>IF(T15=T$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AT15" s="7">
+      <c r="AT15" s="5">
         <f>IF(U15=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU15" s="7">
+      <c r="AU15" s="5">
         <f>IF(V15=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV15" s="7">
+      <c r="AV15" s="5">
         <f>IF(W15=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW15" s="7">
+      <c r="AW15" s="5">
         <f>IF(X15=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX15" s="7">
+      <c r="AX15" s="5">
         <f>IF(Y15=Y$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AY15" s="7">
+      <c r="AY15" s="5">
         <f>IF(Z15=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ15" s="7">
+      <c r="AZ15" s="5">
         <f>IF(AA15=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA15" s="7">
+      <c r="BA15" s="5">
         <f>IF(AB15=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB15" s="7">
+      <c r="BB15" s="5">
         <f>IF(AC15=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC15" s="7">
+      <c r="BC15" s="5">
         <f>IF(AD15=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD15" s="7">
+      <c r="BD15" s="5">
         <f>IF(AE15=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE15" s="7">
+      <c r="BE15" s="5">
         <f>IF(AF15=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -6277,103 +6639,103 @@
       <c r="AF16" s="3">
         <v>3</v>
       </c>
-      <c r="AG16" s="7">
+      <c r="AG16" s="5">
         <f>IF(H16=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH16" s="7">
+      <c r="AH16" s="5">
         <f>IF(I16=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI16" s="7">
+      <c r="AI16" s="5">
         <f>IF(J16=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ16" s="7">
+      <c r="AJ16" s="5">
         <f>IF(K16=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK16" s="7">
+      <c r="AK16" s="5">
         <f>IF(L16=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL16" s="7">
+      <c r="AL16" s="5">
         <f>IF(M16=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM16" s="7">
+      <c r="AM16" s="5">
         <f>IF(N16=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN16" s="7">
+      <c r="AN16" s="5">
         <f>IF(O16=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO16" s="7">
+      <c r="AO16" s="5">
         <f>IF(P16=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP16" s="7">
+      <c r="AP16" s="5">
         <f>IF(Q16=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ16" s="7">
+      <c r="AQ16" s="5">
         <f>IF(R16=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR16" s="7">
+      <c r="AR16" s="5">
         <f>IF(S16=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS16" s="7">
+      <c r="AS16" s="5">
         <f>IF(T16=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT16" s="7">
+      <c r="AT16" s="5">
         <f>IF(U16=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU16" s="7">
+      <c r="AU16" s="5">
         <f>IF(V16=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV16" s="7">
+      <c r="AV16" s="5">
         <f>IF(W16=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW16" s="7">
+      <c r="AW16" s="5">
         <f>IF(X16=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX16" s="7">
+      <c r="AX16" s="5">
         <f>IF(Y16=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY16" s="7">
+      <c r="AY16" s="5">
         <f>IF(Z16=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ16" s="7">
+      <c r="AZ16" s="5">
         <f>IF(AA16=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA16" s="7">
+      <c r="BA16" s="5">
         <f>IF(AB16=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB16" s="7">
+      <c r="BB16" s="5">
         <f>IF(AC16=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC16" s="7">
+      <c r="BC16" s="5">
         <f>IF(AD16=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD16" s="7">
+      <c r="BD16" s="5">
         <f>IF(AE16=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE16" s="7">
+      <c r="BE16" s="5">
         <f>IF(AF16=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -6479,103 +6841,103 @@
       <c r="AF17" s="3">
         <v>4</v>
       </c>
-      <c r="AG17" s="7">
+      <c r="AG17" s="5">
         <f>IF(H17=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH17" s="7">
+      <c r="AH17" s="5">
         <f>IF(I17=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI17" s="7">
+      <c r="AI17" s="5">
         <f>IF(J17=J$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AJ17" s="7">
+      <c r="AJ17" s="5">
         <f>IF(K17=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK17" s="7">
+      <c r="AK17" s="5">
         <f>IF(L17=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL17" s="7">
+      <c r="AL17" s="5">
         <f>IF(M17=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM17" s="7">
+      <c r="AM17" s="5">
         <f>IF(N17=N$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AN17" s="7">
+      <c r="AN17" s="5">
         <f>IF(O17=O$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO17" s="7">
+      <c r="AO17" s="5">
         <f>IF(P17=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP17" s="7">
+      <c r="AP17" s="5">
         <f>IF(Q17=Q$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AQ17" s="7">
+      <c r="AQ17" s="5">
         <f>IF(R17=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR17" s="7">
+      <c r="AR17" s="5">
         <f>IF(S17=S$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS17" s="7">
+      <c r="AS17" s="5">
         <f>IF(T17=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT17" s="7">
+      <c r="AT17" s="5">
         <f>IF(U17=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU17" s="7">
+      <c r="AU17" s="5">
         <f>IF(V17=V$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AV17" s="7">
+      <c r="AV17" s="5">
         <f>IF(W17=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW17" s="7">
+      <c r="AW17" s="5">
         <f>IF(X17=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX17" s="7">
+      <c r="AX17" s="5">
         <f>IF(Y17=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY17" s="7">
+      <c r="AY17" s="5">
         <f>IF(Z17=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ17" s="7">
+      <c r="AZ17" s="5">
         <f>IF(AA17=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA17" s="7">
+      <c r="BA17" s="5">
         <f>IF(AB17=AB$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BB17" s="7">
+      <c r="BB17" s="5">
         <f>IF(AC17=AC$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BC17" s="7">
+      <c r="BC17" s="5">
         <f>IF(AD17=AD$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BD17" s="7">
+      <c r="BD17" s="5">
         <f>IF(AE17=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE17" s="7">
+      <c r="BE17" s="5">
         <f>IF(AF17=AF$47,1,0)</f>
         <v>0</v>
       </c>
@@ -6681,103 +7043,103 @@
       <c r="AF18" s="3">
         <v>3</v>
       </c>
-      <c r="AG18" s="7">
+      <c r="AG18" s="5">
         <f>IF(H18=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH18" s="7">
+      <c r="AH18" s="5">
         <f>IF(I18=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI18" s="7">
+      <c r="AI18" s="5">
         <f>IF(J18=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ18" s="7">
+      <c r="AJ18" s="5">
         <f>IF(K18=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK18" s="7">
+      <c r="AK18" s="5">
         <f>IF(L18=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL18" s="7">
+      <c r="AL18" s="5">
         <f>IF(M18=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM18" s="7">
+      <c r="AM18" s="5">
         <f>IF(N18=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN18" s="7">
+      <c r="AN18" s="5">
         <f>IF(O18=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO18" s="7">
+      <c r="AO18" s="5">
         <f>IF(P18=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP18" s="7">
+      <c r="AP18" s="5">
         <f>IF(Q18=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ18" s="7">
+      <c r="AQ18" s="5">
         <f>IF(R18=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR18" s="7">
+      <c r="AR18" s="5">
         <f>IF(S18=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS18" s="7">
+      <c r="AS18" s="5">
         <f>IF(T18=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT18" s="7">
+      <c r="AT18" s="5">
         <f>IF(U18=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU18" s="7">
+      <c r="AU18" s="5">
         <f>IF(V18=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV18" s="7">
+      <c r="AV18" s="5">
         <f>IF(W18=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW18" s="7">
+      <c r="AW18" s="5">
         <f>IF(X18=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX18" s="7">
+      <c r="AX18" s="5">
         <f>IF(Y18=Y$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AY18" s="7">
+      <c r="AY18" s="5">
         <f>IF(Z18=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ18" s="7">
+      <c r="AZ18" s="5">
         <f>IF(AA18=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA18" s="7">
+      <c r="BA18" s="5">
         <f>IF(AB18=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB18" s="7">
+      <c r="BB18" s="5">
         <f>IF(AC18=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC18" s="7">
+      <c r="BC18" s="5">
         <f>IF(AD18=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD18" s="7">
+      <c r="BD18" s="5">
         <f>IF(AE18=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE18" s="7">
+      <c r="BE18" s="5">
         <f>IF(AF18=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -6883,103 +7245,103 @@
       <c r="AF19" s="3">
         <v>12</v>
       </c>
-      <c r="AG19" s="7">
+      <c r="AG19" s="5">
         <f>IF(H19=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH19" s="7">
+      <c r="AH19" s="5">
         <f>IF(I19=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI19" s="7">
+      <c r="AI19" s="5">
         <f>IF(J19=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ19" s="7">
+      <c r="AJ19" s="5">
         <f>IF(K19=K$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AK19" s="7">
+      <c r="AK19" s="5">
         <f>IF(L19=L$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AL19" s="7">
+      <c r="AL19" s="5">
         <f>IF(M19=M$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AM19" s="7">
+      <c r="AM19" s="5">
         <f>IF(N19=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN19" s="7">
+      <c r="AN19" s="5">
         <f>IF(O19=O$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO19" s="7">
+      <c r="AO19" s="5">
         <f>IF(P19=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP19" s="7">
+      <c r="AP19" s="5">
         <f>IF(Q19=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ19" s="7">
+      <c r="AQ19" s="5">
         <f>IF(R19=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR19" s="7">
+      <c r="AR19" s="5">
         <f>IF(S19=S$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS19" s="7">
+      <c r="AS19" s="5">
         <f>IF(T19=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT19" s="7">
+      <c r="AT19" s="5">
         <f>IF(U19=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU19" s="7">
+      <c r="AU19" s="5">
         <f>IF(V19=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV19" s="7">
+      <c r="AV19" s="5">
         <f>IF(W19=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW19" s="7">
+      <c r="AW19" s="5">
         <f>IF(X19=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX19" s="7">
+      <c r="AX19" s="5">
         <f>IF(Y19=Y$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AY19" s="7">
+      <c r="AY19" s="5">
         <f>IF(Z19=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ19" s="7">
+      <c r="AZ19" s="5">
         <f>IF(AA19=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA19" s="7">
+      <c r="BA19" s="5">
         <f>IF(AB19=AB$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BB19" s="7">
+      <c r="BB19" s="5">
         <f>IF(AC19=AC$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BC19" s="7">
+      <c r="BC19" s="5">
         <f>IF(AD19=AD$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BD19" s="7">
+      <c r="BD19" s="5">
         <f>IF(AE19=AE$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BE19" s="7">
+      <c r="BE19" s="5">
         <f>IF(AF19=AF$47,1,0)</f>
         <v>0</v>
       </c>
@@ -7085,103 +7447,103 @@
       <c r="AF20" s="3">
         <v>3</v>
       </c>
-      <c r="AG20" s="7">
+      <c r="AG20" s="5">
         <f>IF(H20=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH20" s="7">
+      <c r="AH20" s="5">
         <f>IF(I20=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI20" s="7">
+      <c r="AI20" s="5">
         <f>IF(J20=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ20" s="7">
+      <c r="AJ20" s="5">
         <f>IF(K20=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK20" s="7">
+      <c r="AK20" s="5">
         <f>IF(L20=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL20" s="7">
+      <c r="AL20" s="5">
         <f>IF(M20=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM20" s="7">
+      <c r="AM20" s="5">
         <f>IF(N20=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN20" s="7">
+      <c r="AN20" s="5">
         <f>IF(O20=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO20" s="7">
+      <c r="AO20" s="5">
         <f>IF(P20=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP20" s="7">
+      <c r="AP20" s="5">
         <f>IF(Q20=Q$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AQ20" s="7">
+      <c r="AQ20" s="5">
         <f>IF(R20=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR20" s="7">
+      <c r="AR20" s="5">
         <f>IF(S20=S$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS20" s="7">
+      <c r="AS20" s="5">
         <f>IF(T20=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT20" s="7">
+      <c r="AT20" s="5">
         <f>IF(U20=U$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AU20" s="7">
+      <c r="AU20" s="5">
         <f>IF(V20=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV20" s="7">
+      <c r="AV20" s="5">
         <f>IF(W20=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW20" s="7">
+      <c r="AW20" s="5">
         <f>IF(X20=X$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AX20" s="7">
+      <c r="AX20" s="5">
         <f>IF(Y20=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY20" s="7">
+      <c r="AY20" s="5">
         <f>IF(Z20=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ20" s="7">
+      <c r="AZ20" s="5">
         <f>IF(AA20=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA20" s="7">
+      <c r="BA20" s="5">
         <f>IF(AB20=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB20" s="7">
+      <c r="BB20" s="5">
         <f>IF(AC20=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC20" s="7">
+      <c r="BC20" s="5">
         <f>IF(AD20=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD20" s="7">
+      <c r="BD20" s="5">
         <f>IF(AE20=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE20" s="7">
+      <c r="BE20" s="5">
         <f>IF(AF20=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -7287,103 +7649,103 @@
       <c r="AF21" s="3">
         <v>5</v>
       </c>
-      <c r="AG21" s="7">
+      <c r="AG21" s="5">
         <f>IF(H21=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH21" s="7">
+      <c r="AH21" s="5">
         <f>IF(I21=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI21" s="7">
+      <c r="AI21" s="5">
         <f>IF(J21=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ21" s="7">
+      <c r="AJ21" s="5">
         <f>IF(K21=K$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AK21" s="7">
+      <c r="AK21" s="5">
         <f>IF(L21=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL21" s="7">
+      <c r="AL21" s="5">
         <f>IF(M21=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM21" s="7">
+      <c r="AM21" s="5">
         <f>IF(N21=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN21" s="7">
+      <c r="AN21" s="5">
         <f>IF(O21=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO21" s="7">
+      <c r="AO21" s="5">
         <f>IF(P21=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP21" s="7">
+      <c r="AP21" s="5">
         <f>IF(Q21=Q$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AQ21" s="7">
+      <c r="AQ21" s="5">
         <f>IF(R21=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR21" s="7">
+      <c r="AR21" s="5">
         <f>IF(S21=S$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS21" s="7">
+      <c r="AS21" s="5">
         <f>IF(T21=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT21" s="7">
+      <c r="AT21" s="5">
         <f>IF(U21=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU21" s="7">
+      <c r="AU21" s="5">
         <f>IF(V21=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV21" s="7">
+      <c r="AV21" s="5">
         <f>IF(W21=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW21" s="7">
+      <c r="AW21" s="5">
         <f>IF(X21=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX21" s="7">
+      <c r="AX21" s="5">
         <f>IF(Y21=Y$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AY21" s="7">
+      <c r="AY21" s="5">
         <f>IF(Z21=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ21" s="7">
+      <c r="AZ21" s="5">
         <f>IF(AA21=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA21" s="7">
+      <c r="BA21" s="5">
         <f>IF(AB21=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB21" s="7">
+      <c r="BB21" s="5">
         <f>IF(AC21=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC21" s="7">
+      <c r="BC21" s="5">
         <f>IF(AD21=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD21" s="7">
+      <c r="BD21" s="5">
         <f>IF(AE21=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE21" s="7">
+      <c r="BE21" s="5">
         <f>IF(AF21=AF$47,1,0)</f>
         <v>0</v>
       </c>
@@ -7489,103 +7851,103 @@
       <c r="AF22" s="3">
         <v>3</v>
       </c>
-      <c r="AG22" s="7">
+      <c r="AG22" s="5">
         <f>IF(H22=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH22" s="7">
+      <c r="AH22" s="5">
         <f>IF(I22=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI22" s="7">
+      <c r="AI22" s="5">
         <f>IF(J22=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ22" s="7">
+      <c r="AJ22" s="5">
         <f>IF(K22=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK22" s="7">
+      <c r="AK22" s="5">
         <f>IF(L22=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL22" s="7">
+      <c r="AL22" s="5">
         <f>IF(M22=M$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AM22" s="7">
+      <c r="AM22" s="5">
         <f>IF(N22=N$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AN22" s="7">
+      <c r="AN22" s="5">
         <f>IF(O22=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO22" s="7">
+      <c r="AO22" s="5">
         <f>IF(P22=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP22" s="7">
+      <c r="AP22" s="5">
         <f>IF(Q22=Q$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AQ22" s="7">
+      <c r="AQ22" s="5">
         <f>IF(R22=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR22" s="7">
+      <c r="AR22" s="5">
         <f>IF(S22=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS22" s="7">
+      <c r="AS22" s="5">
         <f>IF(T22=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT22" s="7">
+      <c r="AT22" s="5">
         <f>IF(U22=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU22" s="7">
+      <c r="AU22" s="5">
         <f>IF(V22=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV22" s="7">
+      <c r="AV22" s="5">
         <f>IF(W22=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW22" s="7">
+      <c r="AW22" s="5">
         <f>IF(X22=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX22" s="7">
+      <c r="AX22" s="5">
         <f>IF(Y22=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY22" s="7">
+      <c r="AY22" s="5">
         <f>IF(Z22=Z$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AZ22" s="7">
+      <c r="AZ22" s="5">
         <f>IF(AA22=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA22" s="7">
+      <c r="BA22" s="5">
         <f>IF(AB22=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB22" s="7">
+      <c r="BB22" s="5">
         <f>IF(AC22=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC22" s="7">
+      <c r="BC22" s="5">
         <f>IF(AD22=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD22" s="7">
+      <c r="BD22" s="5">
         <f>IF(AE22=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE22" s="7">
+      <c r="BE22" s="5">
         <f>IF(AF22=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -7691,103 +8053,103 @@
       <c r="AF23" s="3">
         <v>3</v>
       </c>
-      <c r="AG23" s="7">
+      <c r="AG23" s="5">
         <f>IF(H23=H$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AH23" s="7">
+      <c r="AH23" s="5">
         <f>IF(I23=I$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AI23" s="7">
+      <c r="AI23" s="5">
         <f>IF(J23=J$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AJ23" s="7">
+      <c r="AJ23" s="5">
         <f>IF(K23=K$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AK23" s="7">
+      <c r="AK23" s="5">
         <f>IF(L23=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL23" s="7">
+      <c r="AL23" s="5">
         <f>IF(M23=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM23" s="7">
+      <c r="AM23" s="5">
         <f>IF(N23=N$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AN23" s="7">
+      <c r="AN23" s="5">
         <f>IF(O23=O$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO23" s="7">
+      <c r="AO23" s="5">
         <f>IF(P23=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP23" s="7">
+      <c r="AP23" s="5">
         <f>IF(Q23=Q$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AQ23" s="7">
+      <c r="AQ23" s="5">
         <f>IF(R23=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR23" s="7">
+      <c r="AR23" s="5">
         <f>IF(S23=S$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS23" s="7">
+      <c r="AS23" s="5">
         <f>IF(T23=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT23" s="7">
+      <c r="AT23" s="5">
         <f>IF(U23=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU23" s="7">
+      <c r="AU23" s="5">
         <f>IF(V23=V$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AV23" s="7">
+      <c r="AV23" s="5">
         <f>IF(W23=W$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AW23" s="7">
+      <c r="AW23" s="5">
         <f>IF(X23=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX23" s="7">
+      <c r="AX23" s="5">
         <f>IF(Y23=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY23" s="7">
+      <c r="AY23" s="5">
         <f>IF(Z23=Z$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AZ23" s="7">
+      <c r="AZ23" s="5">
         <f>IF(AA23=AA$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BA23" s="7">
+      <c r="BA23" s="5">
         <f>IF(AB23=AB$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BB23" s="7">
+      <c r="BB23" s="5">
         <f>IF(AC23=AC$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BC23" s="7">
+      <c r="BC23" s="5">
         <f>IF(AD23=AD$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BD23" s="7">
+      <c r="BD23" s="5">
         <f>IF(AE23=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE23" s="7">
+      <c r="BE23" s="5">
         <f>IF(AF23=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -7893,103 +8255,103 @@
       <c r="AF24" s="3">
         <v>10</v>
       </c>
-      <c r="AG24" s="7">
+      <c r="AG24" s="5">
         <f>IF(H24=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH24" s="7">
+      <c r="AH24" s="5">
         <f>IF(I24=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI24" s="7">
+      <c r="AI24" s="5">
         <f>IF(J24=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ24" s="7">
+      <c r="AJ24" s="5">
         <f>IF(K24=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK24" s="7">
+      <c r="AK24" s="5">
         <f>IF(L24=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL24" s="7">
+      <c r="AL24" s="5">
         <f>IF(M24=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM24" s="7">
+      <c r="AM24" s="5">
         <f>IF(N24=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN24" s="7">
+      <c r="AN24" s="5">
         <f>IF(O24=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO24" s="7">
+      <c r="AO24" s="5">
         <f>IF(P24=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP24" s="7">
+      <c r="AP24" s="5">
         <f>IF(Q24=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ24" s="7">
+      <c r="AQ24" s="5">
         <f>IF(R24=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR24" s="7">
+      <c r="AR24" s="5">
         <f>IF(S24=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS24" s="7">
+      <c r="AS24" s="5">
         <f>IF(T24=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT24" s="7">
+      <c r="AT24" s="5">
         <f>IF(U24=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU24" s="7">
+      <c r="AU24" s="5">
         <f>IF(V24=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV24" s="7">
+      <c r="AV24" s="5">
         <f>IF(W24=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW24" s="7">
+      <c r="AW24" s="5">
         <f>IF(X24=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX24" s="7">
+      <c r="AX24" s="5">
         <f>IF(Y24=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY24" s="7">
+      <c r="AY24" s="5">
         <f>IF(Z24=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ24" s="7">
+      <c r="AZ24" s="5">
         <f>IF(AA24=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA24" s="7">
+      <c r="BA24" s="5">
         <f>IF(AB24=AB$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BB24" s="7">
+      <c r="BB24" s="5">
         <f>IF(AC24=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC24" s="7">
+      <c r="BC24" s="5">
         <f>IF(AD24=AD$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BD24" s="7">
+      <c r="BD24" s="5">
         <f>IF(AE24=AE$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BE24" s="7">
+      <c r="BE24" s="5">
         <f>IF(AF24=AF$47,1,0)</f>
         <v>0</v>
       </c>
@@ -8095,103 +8457,103 @@
       <c r="AF25" s="3">
         <v>3</v>
       </c>
-      <c r="AG25" s="7">
+      <c r="AG25" s="5">
         <f>IF(H25=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH25" s="7">
+      <c r="AH25" s="5">
         <f>IF(I25=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI25" s="7">
+      <c r="AI25" s="5">
         <f>IF(J25=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ25" s="7">
+      <c r="AJ25" s="5">
         <f>IF(K25=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK25" s="7">
+      <c r="AK25" s="5">
         <f>IF(L25=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL25" s="7">
+      <c r="AL25" s="5">
         <f>IF(M25=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM25" s="7">
+      <c r="AM25" s="5">
         <f>IF(N25=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN25" s="7">
+      <c r="AN25" s="5">
         <f>IF(O25=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO25" s="7">
+      <c r="AO25" s="5">
         <f>IF(P25=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP25" s="7">
+      <c r="AP25" s="5">
         <f>IF(Q25=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ25" s="7">
+      <c r="AQ25" s="5">
         <f>IF(R25=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR25" s="7">
+      <c r="AR25" s="5">
         <f>IF(S25=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS25" s="7">
+      <c r="AS25" s="5">
         <f>IF(T25=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT25" s="7">
+      <c r="AT25" s="5">
         <f>IF(U25=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU25" s="7">
+      <c r="AU25" s="5">
         <f>IF(V25=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV25" s="7">
+      <c r="AV25" s="5">
         <f>IF(W25=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW25" s="7">
+      <c r="AW25" s="5">
         <f>IF(X25=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX25" s="7">
+      <c r="AX25" s="5">
         <f>IF(Y25=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY25" s="7">
+      <c r="AY25" s="5">
         <f>IF(Z25=Z$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AZ25" s="7">
+      <c r="AZ25" s="5">
         <f>IF(AA25=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA25" s="7">
+      <c r="BA25" s="5">
         <f>IF(AB25=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB25" s="7">
+      <c r="BB25" s="5">
         <f>IF(AC25=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC25" s="7">
+      <c r="BC25" s="5">
         <f>IF(AD25=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD25" s="7">
+      <c r="BD25" s="5">
         <f>IF(AE25=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE25" s="7">
+      <c r="BE25" s="5">
         <f>IF(AF25=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -8297,103 +8659,103 @@
       <c r="AF26" s="3">
         <v>6</v>
       </c>
-      <c r="AG26" s="7">
+      <c r="AG26" s="5">
         <f>IF(H26=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH26" s="7">
+      <c r="AH26" s="5">
         <f>IF(I26=I$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AI26" s="7">
+      <c r="AI26" s="5">
         <f>IF(J26=J$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AJ26" s="7">
+      <c r="AJ26" s="5">
         <f>IF(K26=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK26" s="7">
+      <c r="AK26" s="5">
         <f>IF(L26=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL26" s="7">
+      <c r="AL26" s="5">
         <f>IF(M26=M$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AM26" s="7">
+      <c r="AM26" s="5">
         <f>IF(N26=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN26" s="7">
+      <c r="AN26" s="5">
         <f>IF(O26=O$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO26" s="7">
+      <c r="AO26" s="5">
         <f>IF(P26=P$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AP26" s="7">
+      <c r="AP26" s="5">
         <f>IF(Q26=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ26" s="7">
+      <c r="AQ26" s="5">
         <f>IF(R26=R$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AR26" s="7">
+      <c r="AR26" s="5">
         <f>IF(S26=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS26" s="7">
+      <c r="AS26" s="5">
         <f>IF(T26=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT26" s="7">
+      <c r="AT26" s="5">
         <f>IF(U26=U$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AU26" s="7">
+      <c r="AU26" s="5">
         <f>IF(V26=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV26" s="7">
+      <c r="AV26" s="5">
         <f>IF(W26=W$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AW26" s="7">
+      <c r="AW26" s="5">
         <f>IF(X26=X$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AX26" s="7">
+      <c r="AX26" s="5">
         <f>IF(Y26=Y$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AY26" s="7">
+      <c r="AY26" s="5">
         <f>IF(Z26=Z$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AZ26" s="7">
+      <c r="AZ26" s="5">
         <f>IF(AA26=AA$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BA26" s="7">
+      <c r="BA26" s="5">
         <f>IF(AB26=AB$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BB26" s="7">
+      <c r="BB26" s="5">
         <f>IF(AC26=AC$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BC26" s="7">
+      <c r="BC26" s="5">
         <f>IF(AD26=AD$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BD26" s="7">
+      <c r="BD26" s="5">
         <f>IF(AE26=AE$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BE26" s="7">
+      <c r="BE26" s="5">
         <f>IF(AF26=AF$47,1,0)</f>
         <v>0</v>
       </c>
@@ -8499,103 +8861,103 @@
       <c r="AF27" s="3">
         <v>3</v>
       </c>
-      <c r="AG27" s="7">
+      <c r="AG27" s="5">
         <f>IF(H27=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH27" s="7">
+      <c r="AH27" s="5">
         <f>IF(I27=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI27" s="7">
+      <c r="AI27" s="5">
         <f>IF(J27=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ27" s="7">
+      <c r="AJ27" s="5">
         <f>IF(K27=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK27" s="7">
+      <c r="AK27" s="5">
         <f>IF(L27=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL27" s="7">
+      <c r="AL27" s="5">
         <f>IF(M27=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM27" s="7">
+      <c r="AM27" s="5">
         <f>IF(N27=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN27" s="7">
+      <c r="AN27" s="5">
         <f>IF(O27=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO27" s="7">
+      <c r="AO27" s="5">
         <f>IF(P27=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP27" s="7">
+      <c r="AP27" s="5">
         <f>IF(Q27=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ27" s="7">
+      <c r="AQ27" s="5">
         <f>IF(R27=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR27" s="7">
+      <c r="AR27" s="5">
         <f>IF(S27=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS27" s="7">
+      <c r="AS27" s="5">
         <f>IF(T27=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT27" s="7">
+      <c r="AT27" s="5">
         <f>IF(U27=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU27" s="7">
+      <c r="AU27" s="5">
         <f>IF(V27=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV27" s="7">
+      <c r="AV27" s="5">
         <f>IF(W27=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW27" s="7">
+      <c r="AW27" s="5">
         <f>IF(X27=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX27" s="7">
+      <c r="AX27" s="5">
         <f>IF(Y27=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY27" s="7">
+      <c r="AY27" s="5">
         <f>IF(Z27=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ27" s="7">
+      <c r="AZ27" s="5">
         <f>IF(AA27=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA27" s="7">
+      <c r="BA27" s="5">
         <f>IF(AB27=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB27" s="7">
+      <c r="BB27" s="5">
         <f>IF(AC27=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC27" s="7">
+      <c r="BC27" s="5">
         <f>IF(AD27=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD27" s="7">
+      <c r="BD27" s="5">
         <f>IF(AE27=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE27" s="7">
+      <c r="BE27" s="5">
         <f>IF(AF27=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -8701,103 +9063,103 @@
       <c r="AF28" s="3">
         <v>3</v>
       </c>
-      <c r="AG28" s="7">
+      <c r="AG28" s="5">
         <f>IF(H28=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH28" s="7">
+      <c r="AH28" s="5">
         <f>IF(I28=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI28" s="7">
+      <c r="AI28" s="5">
         <f>IF(J28=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ28" s="7">
+      <c r="AJ28" s="5">
         <f>IF(K28=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK28" s="7">
+      <c r="AK28" s="5">
         <f>IF(L28=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL28" s="7">
+      <c r="AL28" s="5">
         <f>IF(M28=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM28" s="7">
+      <c r="AM28" s="5">
         <f>IF(N28=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN28" s="7">
+      <c r="AN28" s="5">
         <f>IF(O28=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO28" s="7">
+      <c r="AO28" s="5">
         <f>IF(P28=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP28" s="7">
+      <c r="AP28" s="5">
         <f>IF(Q28=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ28" s="7">
+      <c r="AQ28" s="5">
         <f>IF(R28=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR28" s="7">
+      <c r="AR28" s="5">
         <f>IF(S28=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS28" s="7">
+      <c r="AS28" s="5">
         <f>IF(T28=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT28" s="7">
+      <c r="AT28" s="5">
         <f>IF(U28=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU28" s="7">
+      <c r="AU28" s="5">
         <f>IF(V28=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV28" s="7">
+      <c r="AV28" s="5">
         <f>IF(W28=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW28" s="7">
+      <c r="AW28" s="5">
         <f>IF(X28=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX28" s="7">
+      <c r="AX28" s="5">
         <f>IF(Y28=Y$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AY28" s="7">
+      <c r="AY28" s="5">
         <f>IF(Z28=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ28" s="7">
+      <c r="AZ28" s="5">
         <f>IF(AA28=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA28" s="7">
+      <c r="BA28" s="5">
         <f>IF(AB28=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB28" s="7">
+      <c r="BB28" s="5">
         <f>IF(AC28=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC28" s="7">
+      <c r="BC28" s="5">
         <f>IF(AD28=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD28" s="7">
+      <c r="BD28" s="5">
         <f>IF(AE28=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE28" s="7">
+      <c r="BE28" s="5">
         <f>IF(AF28=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -8903,103 +9265,103 @@
       <c r="AF29" s="3">
         <v>3</v>
       </c>
-      <c r="AG29" s="7">
+      <c r="AG29" s="5">
         <f>IF(H29=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH29" s="7">
+      <c r="AH29" s="5">
         <f>IF(I29=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI29" s="7">
+      <c r="AI29" s="5">
         <f>IF(J29=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ29" s="7">
+      <c r="AJ29" s="5">
         <f>IF(K29=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK29" s="7">
+      <c r="AK29" s="5">
         <f>IF(L29=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL29" s="7">
+      <c r="AL29" s="5">
         <f>IF(M29=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM29" s="7">
+      <c r="AM29" s="5">
         <f>IF(N29=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN29" s="7">
+      <c r="AN29" s="5">
         <f>IF(O29=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO29" s="7">
+      <c r="AO29" s="5">
         <f>IF(P29=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP29" s="7">
+      <c r="AP29" s="5">
         <f>IF(Q29=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ29" s="7">
+      <c r="AQ29" s="5">
         <f>IF(R29=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR29" s="7">
+      <c r="AR29" s="5">
         <f>IF(S29=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS29" s="7">
+      <c r="AS29" s="5">
         <f>IF(T29=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT29" s="7">
+      <c r="AT29" s="5">
         <f>IF(U29=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU29" s="7">
+      <c r="AU29" s="5">
         <f>IF(V29=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV29" s="7">
+      <c r="AV29" s="5">
         <f>IF(W29=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW29" s="7">
+      <c r="AW29" s="5">
         <f>IF(X29=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX29" s="7">
+      <c r="AX29" s="5">
         <f>IF(Y29=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY29" s="7">
+      <c r="AY29" s="5">
         <f>IF(Z29=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ29" s="7">
+      <c r="AZ29" s="5">
         <f>IF(AA29=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA29" s="7">
+      <c r="BA29" s="5">
         <f>IF(AB29=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB29" s="7">
+      <c r="BB29" s="5">
         <f>IF(AC29=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC29" s="7">
+      <c r="BC29" s="5">
         <f>IF(AD29=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD29" s="7">
+      <c r="BD29" s="5">
         <f>IF(AE29=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE29" s="7">
+      <c r="BE29" s="5">
         <f>IF(AF29=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -9105,103 +9467,103 @@
       <c r="AF30" s="3">
         <v>3</v>
       </c>
-      <c r="AG30" s="7">
+      <c r="AG30" s="5">
         <f>IF(H30=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH30" s="7">
+      <c r="AH30" s="5">
         <f>IF(I30=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI30" s="7">
+      <c r="AI30" s="5">
         <f>IF(J30=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ30" s="7">
+      <c r="AJ30" s="5">
         <f>IF(K30=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK30" s="7">
+      <c r="AK30" s="5">
         <f>IF(L30=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL30" s="7">
+      <c r="AL30" s="5">
         <f>IF(M30=M$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AM30" s="7">
+      <c r="AM30" s="5">
         <f>IF(N30=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN30" s="7">
+      <c r="AN30" s="5">
         <f>IF(O30=O$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO30" s="7">
+      <c r="AO30" s="5">
         <f>IF(P30=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP30" s="7">
+      <c r="AP30" s="5">
         <f>IF(Q30=Q$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AQ30" s="7">
+      <c r="AQ30" s="5">
         <f>IF(R30=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR30" s="7">
+      <c r="AR30" s="5">
         <f>IF(S30=S$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS30" s="7">
+      <c r="AS30" s="5">
         <f>IF(T30=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT30" s="7">
+      <c r="AT30" s="5">
         <f>IF(U30=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU30" s="7">
+      <c r="AU30" s="5">
         <f>IF(V30=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV30" s="7">
+      <c r="AV30" s="5">
         <f>IF(W30=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW30" s="7">
+      <c r="AW30" s="5">
         <f>IF(X30=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX30" s="7">
+      <c r="AX30" s="5">
         <f>IF(Y30=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY30" s="7">
+      <c r="AY30" s="5">
         <f>IF(Z30=Z$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AZ30" s="7">
+      <c r="AZ30" s="5">
         <f>IF(AA30=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA30" s="7">
+      <c r="BA30" s="5">
         <f>IF(AB30=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB30" s="7">
+      <c r="BB30" s="5">
         <f>IF(AC30=AC$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BC30" s="7">
+      <c r="BC30" s="5">
         <f>IF(AD30=AD$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BD30" s="7">
+      <c r="BD30" s="5">
         <f>IF(AE30=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE30" s="7">
+      <c r="BE30" s="5">
         <f>IF(AF30=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -9307,103 +9669,103 @@
       <c r="AF31" s="3">
         <v>3</v>
       </c>
-      <c r="AG31" s="7">
+      <c r="AG31" s="5">
         <f>IF(H31=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH31" s="7">
+      <c r="AH31" s="5">
         <f>IF(I31=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI31" s="7">
+      <c r="AI31" s="5">
         <f>IF(J31=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ31" s="7">
+      <c r="AJ31" s="5">
         <f>IF(K31=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK31" s="7">
+      <c r="AK31" s="5">
         <f>IF(L31=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL31" s="7">
+      <c r="AL31" s="5">
         <f>IF(M31=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM31" s="7">
+      <c r="AM31" s="5">
         <f>IF(N31=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN31" s="7">
+      <c r="AN31" s="5">
         <f>IF(O31=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO31" s="7">
+      <c r="AO31" s="5">
         <f>IF(P31=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP31" s="7">
+      <c r="AP31" s="5">
         <f>IF(Q31=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ31" s="7">
+      <c r="AQ31" s="5">
         <f>IF(R31=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR31" s="7">
+      <c r="AR31" s="5">
         <f>IF(S31=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS31" s="7">
+      <c r="AS31" s="5">
         <f>IF(T31=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT31" s="7">
+      <c r="AT31" s="5">
         <f>IF(U31=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU31" s="7">
+      <c r="AU31" s="5">
         <f>IF(V31=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV31" s="7">
+      <c r="AV31" s="5">
         <f>IF(W31=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW31" s="7">
+      <c r="AW31" s="5">
         <f>IF(X31=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX31" s="7">
+      <c r="AX31" s="5">
         <f>IF(Y31=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY31" s="7">
+      <c r="AY31" s="5">
         <f>IF(Z31=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ31" s="7">
+      <c r="AZ31" s="5">
         <f>IF(AA31=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA31" s="7">
+      <c r="BA31" s="5">
         <f>IF(AB31=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB31" s="7">
+      <c r="BB31" s="5">
         <f>IF(AC31=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC31" s="7">
+      <c r="BC31" s="5">
         <f>IF(AD31=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD31" s="7">
+      <c r="BD31" s="5">
         <f>IF(AE31=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE31" s="7">
+      <c r="BE31" s="5">
         <f>IF(AF31=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -9509,103 +9871,103 @@
       <c r="AF32" s="3">
         <v>3</v>
       </c>
-      <c r="AG32" s="7">
+      <c r="AG32" s="5">
         <f>IF(H32=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH32" s="7">
+      <c r="AH32" s="5">
         <f>IF(I32=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI32" s="7">
+      <c r="AI32" s="5">
         <f>IF(J32=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ32" s="7">
+      <c r="AJ32" s="5">
         <f>IF(K32=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK32" s="7">
+      <c r="AK32" s="5">
         <f>IF(L32=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL32" s="7">
+      <c r="AL32" s="5">
         <f>IF(M32=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM32" s="7">
+      <c r="AM32" s="5">
         <f>IF(N32=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN32" s="7">
+      <c r="AN32" s="5">
         <f>IF(O32=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO32" s="7">
+      <c r="AO32" s="5">
         <f>IF(P32=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP32" s="7">
+      <c r="AP32" s="5">
         <f>IF(Q32=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ32" s="7">
+      <c r="AQ32" s="5">
         <f>IF(R32=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR32" s="7">
+      <c r="AR32" s="5">
         <f>IF(S32=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS32" s="7">
+      <c r="AS32" s="5">
         <f>IF(T32=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT32" s="7">
+      <c r="AT32" s="5">
         <f>IF(U32=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU32" s="7">
+      <c r="AU32" s="5">
         <f>IF(V32=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV32" s="7">
+      <c r="AV32" s="5">
         <f>IF(W32=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW32" s="7">
+      <c r="AW32" s="5">
         <f>IF(X32=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX32" s="7">
+      <c r="AX32" s="5">
         <f>IF(Y32=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY32" s="7">
+      <c r="AY32" s="5">
         <f>IF(Z32=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ32" s="7">
+      <c r="AZ32" s="5">
         <f>IF(AA32=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA32" s="7">
+      <c r="BA32" s="5">
         <f>IF(AB32=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB32" s="7">
+      <c r="BB32" s="5">
         <f>IF(AC32=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC32" s="7">
+      <c r="BC32" s="5">
         <f>IF(AD32=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD32" s="7">
+      <c r="BD32" s="5">
         <f>IF(AE32=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE32" s="7">
+      <c r="BE32" s="5">
         <f>IF(AF32=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -9711,103 +10073,103 @@
       <c r="AF33" s="3">
         <v>3</v>
       </c>
-      <c r="AG33" s="7">
+      <c r="AG33" s="5">
         <f>IF(H33=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH33" s="7">
+      <c r="AH33" s="5">
         <f>IF(I33=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI33" s="7">
+      <c r="AI33" s="5">
         <f>IF(J33=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ33" s="7">
+      <c r="AJ33" s="5">
         <f>IF(K33=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK33" s="7">
+      <c r="AK33" s="5">
         <f>IF(L33=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL33" s="7">
+      <c r="AL33" s="5">
         <f>IF(M33=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM33" s="7">
+      <c r="AM33" s="5">
         <f>IF(N33=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN33" s="7">
+      <c r="AN33" s="5">
         <f>IF(O33=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO33" s="7">
+      <c r="AO33" s="5">
         <f>IF(P33=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP33" s="7">
+      <c r="AP33" s="5">
         <f>IF(Q33=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ33" s="7">
+      <c r="AQ33" s="5">
         <f>IF(R33=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR33" s="7">
+      <c r="AR33" s="5">
         <f>IF(S33=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS33" s="7">
+      <c r="AS33" s="5">
         <f>IF(T33=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT33" s="7">
+      <c r="AT33" s="5">
         <f>IF(U33=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU33" s="7">
+      <c r="AU33" s="5">
         <f>IF(V33=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV33" s="7">
+      <c r="AV33" s="5">
         <f>IF(W33=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW33" s="7">
+      <c r="AW33" s="5">
         <f>IF(X33=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX33" s="7">
+      <c r="AX33" s="5">
         <f>IF(Y33=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY33" s="7">
+      <c r="AY33" s="5">
         <f>IF(Z33=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ33" s="7">
+      <c r="AZ33" s="5">
         <f>IF(AA33=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA33" s="7">
+      <c r="BA33" s="5">
         <f>IF(AB33=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB33" s="7">
+      <c r="BB33" s="5">
         <f>IF(AC33=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC33" s="7">
+      <c r="BC33" s="5">
         <f>IF(AD33=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD33" s="7">
+      <c r="BD33" s="5">
         <f>IF(AE33=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE33" s="7">
+      <c r="BE33" s="5">
         <f>IF(AF33=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -9913,103 +10275,103 @@
       <c r="AF34" s="3">
         <v>3</v>
       </c>
-      <c r="AG34" s="7">
+      <c r="AG34" s="5">
         <f>IF(H34=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH34" s="7">
+      <c r="AH34" s="5">
         <f>IF(I34=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI34" s="7">
+      <c r="AI34" s="5">
         <f>IF(J34=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ34" s="7">
+      <c r="AJ34" s="5">
         <f>IF(K34=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK34" s="7">
+      <c r="AK34" s="5">
         <f>IF(L34=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL34" s="7">
+      <c r="AL34" s="5">
         <f>IF(M34=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM34" s="7">
+      <c r="AM34" s="5">
         <f>IF(N34=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN34" s="7">
+      <c r="AN34" s="5">
         <f>IF(O34=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO34" s="7">
+      <c r="AO34" s="5">
         <f>IF(P34=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP34" s="7">
+      <c r="AP34" s="5">
         <f>IF(Q34=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ34" s="7">
+      <c r="AQ34" s="5">
         <f>IF(R34=R$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AR34" s="7">
+      <c r="AR34" s="5">
         <f>IF(S34=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS34" s="7">
+      <c r="AS34" s="5">
         <f>IF(T34=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT34" s="7">
+      <c r="AT34" s="5">
         <f>IF(U34=U$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AU34" s="7">
+      <c r="AU34" s="5">
         <f>IF(V34=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV34" s="7">
+      <c r="AV34" s="5">
         <f>IF(W34=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW34" s="7">
+      <c r="AW34" s="5">
         <f>IF(X34=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX34" s="7">
+      <c r="AX34" s="5">
         <f>IF(Y34=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY34" s="7">
+      <c r="AY34" s="5">
         <f>IF(Z34=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ34" s="7">
+      <c r="AZ34" s="5">
         <f>IF(AA34=AA$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BA34" s="7">
+      <c r="BA34" s="5">
         <f>IF(AB34=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB34" s="7">
+      <c r="BB34" s="5">
         <f>IF(AC34=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC34" s="7">
+      <c r="BC34" s="5">
         <f>IF(AD34=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD34" s="7">
+      <c r="BD34" s="5">
         <f>IF(AE34=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE34" s="7">
+      <c r="BE34" s="5">
         <f>IF(AF34=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -10115,103 +10477,103 @@
       <c r="AF35" s="3">
         <v>3</v>
       </c>
-      <c r="AG35" s="7">
+      <c r="AG35" s="5">
         <f>IF(H35=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH35" s="7">
+      <c r="AH35" s="5">
         <f>IF(I35=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI35" s="7">
+      <c r="AI35" s="5">
         <f>IF(J35=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ35" s="7">
+      <c r="AJ35" s="5">
         <f>IF(K35=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK35" s="7">
+      <c r="AK35" s="5">
         <f>IF(L35=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL35" s="7">
+      <c r="AL35" s="5">
         <f>IF(M35=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM35" s="7">
+      <c r="AM35" s="5">
         <f>IF(N35=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN35" s="7">
+      <c r="AN35" s="5">
         <f>IF(O35=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO35" s="7">
+      <c r="AO35" s="5">
         <f>IF(P35=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP35" s="7">
+      <c r="AP35" s="5">
         <f>IF(Q35=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ35" s="7">
+      <c r="AQ35" s="5">
         <f>IF(R35=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR35" s="7">
+      <c r="AR35" s="5">
         <f>IF(S35=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS35" s="7">
+      <c r="AS35" s="5">
         <f>IF(T35=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT35" s="7">
+      <c r="AT35" s="5">
         <f>IF(U35=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU35" s="7">
+      <c r="AU35" s="5">
         <f>IF(V35=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV35" s="7">
+      <c r="AV35" s="5">
         <f>IF(W35=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW35" s="7">
+      <c r="AW35" s="5">
         <f>IF(X35=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX35" s="7">
+      <c r="AX35" s="5">
         <f>IF(Y35=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY35" s="7">
+      <c r="AY35" s="5">
         <f>IF(Z35=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ35" s="7">
+      <c r="AZ35" s="5">
         <f>IF(AA35=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA35" s="7">
+      <c r="BA35" s="5">
         <f>IF(AB35=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB35" s="7">
+      <c r="BB35" s="5">
         <f>IF(AC35=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC35" s="7">
+      <c r="BC35" s="5">
         <f>IF(AD35=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD35" s="7">
+      <c r="BD35" s="5">
         <f>IF(AE35=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE35" s="7">
+      <c r="BE35" s="5">
         <f>IF(AF35=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -10317,103 +10679,103 @@
       <c r="AF36" s="3">
         <v>3</v>
       </c>
-      <c r="AG36" s="7">
+      <c r="AG36" s="5">
         <f>IF(H36=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH36" s="7">
+      <c r="AH36" s="5">
         <f>IF(I36=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI36" s="7">
+      <c r="AI36" s="5">
         <f>IF(J36=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ36" s="7">
+      <c r="AJ36" s="5">
         <f>IF(K36=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK36" s="7">
+      <c r="AK36" s="5">
         <f>IF(L36=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL36" s="7">
+      <c r="AL36" s="5">
         <f>IF(M36=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM36" s="7">
+      <c r="AM36" s="5">
         <f>IF(N36=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN36" s="7">
+      <c r="AN36" s="5">
         <f>IF(O36=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO36" s="7">
+      <c r="AO36" s="5">
         <f>IF(P36=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP36" s="7">
+      <c r="AP36" s="5">
         <f>IF(Q36=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ36" s="7">
+      <c r="AQ36" s="5">
         <f>IF(R36=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR36" s="7">
+      <c r="AR36" s="5">
         <f>IF(S36=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS36" s="7">
+      <c r="AS36" s="5">
         <f>IF(T36=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT36" s="7">
+      <c r="AT36" s="5">
         <f>IF(U36=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU36" s="7">
+      <c r="AU36" s="5">
         <f>IF(V36=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV36" s="7">
+      <c r="AV36" s="5">
         <f>IF(W36=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW36" s="7">
+      <c r="AW36" s="5">
         <f>IF(X36=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX36" s="7">
+      <c r="AX36" s="5">
         <f>IF(Y36=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY36" s="7">
+      <c r="AY36" s="5">
         <f>IF(Z36=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ36" s="7">
+      <c r="AZ36" s="5">
         <f>IF(AA36=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA36" s="7">
+      <c r="BA36" s="5">
         <f>IF(AB36=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB36" s="7">
+      <c r="BB36" s="5">
         <f>IF(AC36=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC36" s="7">
+      <c r="BC36" s="5">
         <f>IF(AD36=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD36" s="7">
+      <c r="BD36" s="5">
         <f>IF(AE36=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE36" s="7">
+      <c r="BE36" s="5">
         <f>IF(AF36=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -10519,103 +10881,103 @@
       <c r="AF37" s="3">
         <v>3</v>
       </c>
-      <c r="AG37" s="7">
+      <c r="AG37" s="5">
         <f>IF(H37=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH37" s="7">
+      <c r="AH37" s="5">
         <f>IF(I37=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI37" s="7">
+      <c r="AI37" s="5">
         <f>IF(J37=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ37" s="7">
+      <c r="AJ37" s="5">
         <f>IF(K37=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK37" s="7">
+      <c r="AK37" s="5">
         <f>IF(L37=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL37" s="7">
+      <c r="AL37" s="5">
         <f>IF(M37=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM37" s="7">
+      <c r="AM37" s="5">
         <f>IF(N37=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN37" s="7">
+      <c r="AN37" s="5">
         <f>IF(O37=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO37" s="7">
+      <c r="AO37" s="5">
         <f>IF(P37=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP37" s="7">
+      <c r="AP37" s="5">
         <f>IF(Q37=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ37" s="7">
+      <c r="AQ37" s="5">
         <f>IF(R37=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR37" s="7">
+      <c r="AR37" s="5">
         <f>IF(S37=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS37" s="7">
+      <c r="AS37" s="5">
         <f>IF(T37=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT37" s="7">
+      <c r="AT37" s="5">
         <f>IF(U37=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU37" s="7">
+      <c r="AU37" s="5">
         <f>IF(V37=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV37" s="7">
+      <c r="AV37" s="5">
         <f>IF(W37=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW37" s="7">
+      <c r="AW37" s="5">
         <f>IF(X37=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX37" s="7">
+      <c r="AX37" s="5">
         <f>IF(Y37=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY37" s="7">
+      <c r="AY37" s="5">
         <f>IF(Z37=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ37" s="7">
+      <c r="AZ37" s="5">
         <f>IF(AA37=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA37" s="7">
+      <c r="BA37" s="5">
         <f>IF(AB37=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB37" s="7">
+      <c r="BB37" s="5">
         <f>IF(AC37=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC37" s="7">
+      <c r="BC37" s="5">
         <f>IF(AD37=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD37" s="7">
+      <c r="BD37" s="5">
         <f>IF(AE37=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE37" s="7">
+      <c r="BE37" s="5">
         <f>IF(AF37=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -10721,103 +11083,103 @@
       <c r="AF38" s="3">
         <v>3</v>
       </c>
-      <c r="AG38" s="7">
+      <c r="AG38" s="5">
         <f>IF(H38=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH38" s="7">
+      <c r="AH38" s="5">
         <f>IF(I38=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI38" s="7">
+      <c r="AI38" s="5">
         <f>IF(J38=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ38" s="7">
+      <c r="AJ38" s="5">
         <f>IF(K38=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK38" s="7">
+      <c r="AK38" s="5">
         <f>IF(L38=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL38" s="7">
+      <c r="AL38" s="5">
         <f>IF(M38=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM38" s="7">
+      <c r="AM38" s="5">
         <f>IF(N38=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN38" s="7">
+      <c r="AN38" s="5">
         <f>IF(O38=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO38" s="7">
+      <c r="AO38" s="5">
         <f>IF(P38=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP38" s="7">
+      <c r="AP38" s="5">
         <f>IF(Q38=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ38" s="7">
+      <c r="AQ38" s="5">
         <f>IF(R38=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR38" s="7">
+      <c r="AR38" s="5">
         <f>IF(S38=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS38" s="7">
+      <c r="AS38" s="5">
         <f>IF(T38=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT38" s="7">
+      <c r="AT38" s="5">
         <f>IF(U38=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU38" s="7">
+      <c r="AU38" s="5">
         <f>IF(V38=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV38" s="7">
+      <c r="AV38" s="5">
         <f>IF(W38=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW38" s="7">
+      <c r="AW38" s="5">
         <f>IF(X38=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX38" s="7">
+      <c r="AX38" s="5">
         <f>IF(Y38=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY38" s="7">
+      <c r="AY38" s="5">
         <f>IF(Z38=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ38" s="7">
+      <c r="AZ38" s="5">
         <f>IF(AA38=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA38" s="7">
+      <c r="BA38" s="5">
         <f>IF(AB38=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB38" s="7">
+      <c r="BB38" s="5">
         <f>IF(AC38=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC38" s="7">
+      <c r="BC38" s="5">
         <f>IF(AD38=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD38" s="7">
+      <c r="BD38" s="5">
         <f>IF(AE38=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE38" s="7">
+      <c r="BE38" s="5">
         <f>IF(AF38=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -10923,103 +11285,103 @@
       <c r="AF39" s="3">
         <v>14</v>
       </c>
-      <c r="AG39" s="7">
+      <c r="AG39" s="5">
         <f>IF(H39=H$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AH39" s="7">
+      <c r="AH39" s="5">
         <f>IF(I39=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI39" s="7">
+      <c r="AI39" s="5">
         <f>IF(J39=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ39" s="7">
+      <c r="AJ39" s="5">
         <f>IF(K39=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK39" s="7">
+      <c r="AK39" s="5">
         <f>IF(L39=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL39" s="7">
+      <c r="AL39" s="5">
         <f>IF(M39=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM39" s="7">
+      <c r="AM39" s="5">
         <f>IF(N39=N$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AN39" s="7">
+      <c r="AN39" s="5">
         <f>IF(O39=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO39" s="7">
+      <c r="AO39" s="5">
         <f>IF(P39=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP39" s="7">
+      <c r="AP39" s="5">
         <f>IF(Q39=Q$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AQ39" s="7">
+      <c r="AQ39" s="5">
         <f>IF(R39=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR39" s="7">
+      <c r="AR39" s="5">
         <f>IF(S39=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS39" s="7">
+      <c r="AS39" s="5">
         <f>IF(T39=T$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AT39" s="7">
+      <c r="AT39" s="5">
         <f>IF(U39=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU39" s="7">
+      <c r="AU39" s="5">
         <f>IF(V39=V$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AV39" s="7">
+      <c r="AV39" s="5">
         <f>IF(W39=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW39" s="7">
+      <c r="AW39" s="5">
         <f>IF(X39=X$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AX39" s="7">
+      <c r="AX39" s="5">
         <f>IF(Y39=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY39" s="7">
+      <c r="AY39" s="5">
         <f>IF(Z39=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ39" s="7">
+      <c r="AZ39" s="5">
         <f>IF(AA39=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA39" s="7">
+      <c r="BA39" s="5">
         <f>IF(AB39=AB$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BB39" s="7">
+      <c r="BB39" s="5">
         <f>IF(AC39=AC$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BC39" s="7">
+      <c r="BC39" s="5">
         <f>IF(AD39=AD$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BD39" s="7">
+      <c r="BD39" s="5">
         <f>IF(AE39=AE$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BE39" s="7">
+      <c r="BE39" s="5">
         <f>IF(AF39=AF$47,1,0)</f>
         <v>0</v>
       </c>
@@ -11125,103 +11487,103 @@
       <c r="AF40" s="3">
         <v>3</v>
       </c>
-      <c r="AG40" s="7">
+      <c r="AG40" s="5">
         <f>IF(H40=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH40" s="7">
+      <c r="AH40" s="5">
         <f>IF(I40=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI40" s="7">
+      <c r="AI40" s="5">
         <f>IF(J40=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ40" s="7">
+      <c r="AJ40" s="5">
         <f>IF(K40=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK40" s="7">
+      <c r="AK40" s="5">
         <f>IF(L40=L$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AL40" s="7">
+      <c r="AL40" s="5">
         <f>IF(M40=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM40" s="7">
+      <c r="AM40" s="5">
         <f>IF(N40=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN40" s="7">
+      <c r="AN40" s="5">
         <f>IF(O40=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO40" s="7">
+      <c r="AO40" s="5">
         <f>IF(P40=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP40" s="7">
+      <c r="AP40" s="5">
         <f>IF(Q40=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ40" s="7">
+      <c r="AQ40" s="5">
         <f>IF(R40=R$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AR40" s="7">
+      <c r="AR40" s="5">
         <f>IF(S40=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS40" s="7">
+      <c r="AS40" s="5">
         <f>IF(T40=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT40" s="7">
+      <c r="AT40" s="5">
         <f>IF(U40=U$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AU40" s="7">
+      <c r="AU40" s="5">
         <f>IF(V40=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV40" s="7">
+      <c r="AV40" s="5">
         <f>IF(W40=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW40" s="7">
+      <c r="AW40" s="5">
         <f>IF(X40=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX40" s="7">
+      <c r="AX40" s="5">
         <f>IF(Y40=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY40" s="7">
+      <c r="AY40" s="5">
         <f>IF(Z40=Z$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AZ40" s="7">
+      <c r="AZ40" s="5">
         <f>IF(AA40=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA40" s="7">
+      <c r="BA40" s="5">
         <f>IF(AB40=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB40" s="7">
+      <c r="BB40" s="5">
         <f>IF(AC40=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC40" s="7">
+      <c r="BC40" s="5">
         <f>IF(AD40=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD40" s="7">
+      <c r="BD40" s="5">
         <f>IF(AE40=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE40" s="7">
+      <c r="BE40" s="5">
         <f>IF(AF40=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -11327,103 +11689,103 @@
       <c r="AF41" s="3">
         <v>3</v>
       </c>
-      <c r="AG41" s="7">
+      <c r="AG41" s="5">
         <f>IF(H41=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH41" s="7">
+      <c r="AH41" s="5">
         <f>IF(I41=I$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AI41" s="7">
+      <c r="AI41" s="5">
         <f>IF(J41=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ41" s="7">
+      <c r="AJ41" s="5">
         <f>IF(K41=K$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AK41" s="7">
+      <c r="AK41" s="5">
         <f>IF(L41=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL41" s="7">
+      <c r="AL41" s="5">
         <f>IF(M41=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM41" s="7">
+      <c r="AM41" s="5">
         <f>IF(N41=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN41" s="7">
+      <c r="AN41" s="5">
         <f>IF(O41=O$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO41" s="7">
+      <c r="AO41" s="5">
         <f>IF(P41=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP41" s="7">
+      <c r="AP41" s="5">
         <f>IF(Q41=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ41" s="7">
+      <c r="AQ41" s="5">
         <f>IF(R41=R$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AR41" s="7">
+      <c r="AR41" s="5">
         <f>IF(S41=S$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS41" s="7">
+      <c r="AS41" s="5">
         <f>IF(T41=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT41" s="7">
+      <c r="AT41" s="5">
         <f>IF(U41=U$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AU41" s="7">
+      <c r="AU41" s="5">
         <f>IF(V41=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV41" s="7">
+      <c r="AV41" s="5">
         <f>IF(W41=W$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AW41" s="7">
+      <c r="AW41" s="5">
         <f>IF(X41=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX41" s="7">
+      <c r="AX41" s="5">
         <f>IF(Y41=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY41" s="7">
+      <c r="AY41" s="5">
         <f>IF(Z41=Z$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AZ41" s="7">
+      <c r="AZ41" s="5">
         <f>IF(AA41=AA$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BA41" s="7">
+      <c r="BA41" s="5">
         <f>IF(AB41=AB$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BB41" s="7">
+      <c r="BB41" s="5">
         <f>IF(AC41=AC$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BC41" s="7">
+      <c r="BC41" s="5">
         <f>IF(AD41=AD$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BD41" s="7">
+      <c r="BD41" s="5">
         <f>IF(AE41=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE41" s="7">
+      <c r="BE41" s="5">
         <f>IF(AF41=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -11529,103 +11891,103 @@
       <c r="AF42" s="3">
         <v>3</v>
       </c>
-      <c r="AG42" s="7">
+      <c r="AG42" s="5">
         <f>IF(H42=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH42" s="7">
+      <c r="AH42" s="5">
         <f>IF(I42=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI42" s="7">
+      <c r="AI42" s="5">
         <f>IF(J42=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ42" s="7">
+      <c r="AJ42" s="5">
         <f>IF(K42=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK42" s="7">
+      <c r="AK42" s="5">
         <f>IF(L42=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL42" s="7">
+      <c r="AL42" s="5">
         <f>IF(M42=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM42" s="7">
+      <c r="AM42" s="5">
         <f>IF(N42=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN42" s="7">
+      <c r="AN42" s="5">
         <f>IF(O42=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO42" s="7">
+      <c r="AO42" s="5">
         <f>IF(P42=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP42" s="7">
+      <c r="AP42" s="5">
         <f>IF(Q42=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ42" s="7">
+      <c r="AQ42" s="5">
         <f>IF(R42=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR42" s="7">
+      <c r="AR42" s="5">
         <f>IF(S42=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS42" s="7">
+      <c r="AS42" s="5">
         <f>IF(T42=T$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AT42" s="7">
+      <c r="AT42" s="5">
         <f>IF(U42=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU42" s="7">
+      <c r="AU42" s="5">
         <f>IF(V42=V$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AV42" s="7">
+      <c r="AV42" s="5">
         <f>IF(W42=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW42" s="7">
+      <c r="AW42" s="5">
         <f>IF(X42=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX42" s="7">
+      <c r="AX42" s="5">
         <f>IF(Y42=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY42" s="7">
+      <c r="AY42" s="5">
         <f>IF(Z42=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ42" s="7">
+      <c r="AZ42" s="5">
         <f>IF(AA42=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA42" s="7">
+      <c r="BA42" s="5">
         <f>IF(AB42=AB$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BB42" s="7">
+      <c r="BB42" s="5">
         <f>IF(AC42=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC42" s="7">
+      <c r="BC42" s="5">
         <f>IF(AD42=AD$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BD42" s="7">
+      <c r="BD42" s="5">
         <f>IF(AE42=AE$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BE42" s="7">
+      <c r="BE42" s="5">
         <f>IF(AF42=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -11731,103 +12093,103 @@
       <c r="AF43" s="3">
         <v>3</v>
       </c>
-      <c r="AG43" s="7">
+      <c r="AG43" s="5">
         <f>IF(H43=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH43" s="7">
+      <c r="AH43" s="5">
         <f>IF(I43=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI43" s="7">
+      <c r="AI43" s="5">
         <f>IF(J43=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ43" s="7">
+      <c r="AJ43" s="5">
         <f>IF(K43=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK43" s="7">
+      <c r="AK43" s="5">
         <f>IF(L43=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL43" s="7">
+      <c r="AL43" s="5">
         <f>IF(M43=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM43" s="7">
+      <c r="AM43" s="5">
         <f>IF(N43=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN43" s="7">
+      <c r="AN43" s="5">
         <f>IF(O43=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO43" s="7">
+      <c r="AO43" s="5">
         <f>IF(P43=P$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AP43" s="7">
+      <c r="AP43" s="5">
         <f>IF(Q43=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ43" s="7">
+      <c r="AQ43" s="5">
         <f>IF(R43=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR43" s="7">
+      <c r="AR43" s="5">
         <f>IF(S43=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS43" s="7">
+      <c r="AS43" s="5">
         <f>IF(T43=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT43" s="7">
+      <c r="AT43" s="5">
         <f>IF(U43=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU43" s="7">
+      <c r="AU43" s="5">
         <f>IF(V43=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV43" s="7">
+      <c r="AV43" s="5">
         <f>IF(W43=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW43" s="7">
+      <c r="AW43" s="5">
         <f>IF(X43=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX43" s="7">
+      <c r="AX43" s="5">
         <f>IF(Y43=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY43" s="7">
+      <c r="AY43" s="5">
         <f>IF(Z43=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ43" s="7">
+      <c r="AZ43" s="5">
         <f>IF(AA43=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA43" s="7">
+      <c r="BA43" s="5">
         <f>IF(AB43=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB43" s="7">
+      <c r="BB43" s="5">
         <f>IF(AC43=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC43" s="7">
+      <c r="BC43" s="5">
         <f>IF(AD43=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD43" s="7">
+      <c r="BD43" s="5">
         <f>IF(AE43=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE43" s="7">
+      <c r="BE43" s="5">
         <f>IF(AF43=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -11933,103 +12295,103 @@
       <c r="AF44" s="3">
         <v>3</v>
       </c>
-      <c r="AG44" s="7">
+      <c r="AG44" s="5">
         <f>IF(H44=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH44" s="7">
+      <c r="AH44" s="5">
         <f>IF(I44=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI44" s="7">
+      <c r="AI44" s="5">
         <f>IF(J44=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ44" s="7">
+      <c r="AJ44" s="5">
         <f>IF(K44=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK44" s="7">
+      <c r="AK44" s="5">
         <f>IF(L44=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL44" s="7">
+      <c r="AL44" s="5">
         <f>IF(M44=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM44" s="7">
+      <c r="AM44" s="5">
         <f>IF(N44=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN44" s="7">
+      <c r="AN44" s="5">
         <f>IF(O44=O$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO44" s="7">
+      <c r="AO44" s="5">
         <f>IF(P44=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP44" s="7">
+      <c r="AP44" s="5">
         <f>IF(Q44=Q$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AQ44" s="7">
+      <c r="AQ44" s="5">
         <f>IF(R44=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR44" s="7">
+      <c r="AR44" s="5">
         <f>IF(S44=S$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS44" s="7">
+      <c r="AS44" s="5">
         <f>IF(T44=T$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AT44" s="7">
+      <c r="AT44" s="5">
         <f>IF(U44=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU44" s="7">
+      <c r="AU44" s="5">
         <f>IF(V44=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV44" s="7">
+      <c r="AV44" s="5">
         <f>IF(W44=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW44" s="7">
+      <c r="AW44" s="5">
         <f>IF(X44=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX44" s="7">
+      <c r="AX44" s="5">
         <f>IF(Y44=Y$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AY44" s="7">
+      <c r="AY44" s="5">
         <f>IF(Z44=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ44" s="7">
+      <c r="AZ44" s="5">
         <f>IF(AA44=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA44" s="7">
+      <c r="BA44" s="5">
         <f>IF(AB44=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB44" s="7">
+      <c r="BB44" s="5">
         <f>IF(AC44=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC44" s="7">
+      <c r="BC44" s="5">
         <f>IF(AD44=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD44" s="7">
+      <c r="BD44" s="5">
         <f>IF(AE44=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE44" s="7">
+      <c r="BE44" s="5">
         <f>IF(AF44=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -12135,103 +12497,103 @@
       <c r="AF45" s="3">
         <v>3</v>
       </c>
-      <c r="AG45" s="7">
+      <c r="AG45" s="5">
         <f>IF(H45=H$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH45" s="7">
+      <c r="AH45" s="5">
         <f>IF(I45=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI45" s="7">
+      <c r="AI45" s="5">
         <f>IF(J45=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ45" s="7">
+      <c r="AJ45" s="5">
         <f>IF(K45=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK45" s="7">
+      <c r="AK45" s="5">
         <f>IF(L45=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL45" s="7">
+      <c r="AL45" s="5">
         <f>IF(M45=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM45" s="7">
+      <c r="AM45" s="5">
         <f>IF(N45=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN45" s="7">
+      <c r="AN45" s="5">
         <f>IF(O45=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO45" s="7">
+      <c r="AO45" s="5">
         <f>IF(P45=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP45" s="7">
+      <c r="AP45" s="5">
         <f>IF(Q45=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ45" s="7">
+      <c r="AQ45" s="5">
         <f>IF(R45=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR45" s="7">
+      <c r="AR45" s="5">
         <f>IF(S45=S$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS45" s="7">
+      <c r="AS45" s="5">
         <f>IF(T45=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT45" s="7">
+      <c r="AT45" s="5">
         <f>IF(U45=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU45" s="7">
+      <c r="AU45" s="5">
         <f>IF(V45=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV45" s="7">
+      <c r="AV45" s="5">
         <f>IF(W45=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW45" s="7">
+      <c r="AW45" s="5">
         <f>IF(X45=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX45" s="7">
+      <c r="AX45" s="5">
         <f>IF(Y45=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY45" s="7">
+      <c r="AY45" s="5">
         <f>IF(Z45=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ45" s="7">
+      <c r="AZ45" s="5">
         <f>IF(AA45=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA45" s="7">
+      <c r="BA45" s="5">
         <f>IF(AB45=AB$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB45" s="7">
+      <c r="BB45" s="5">
         <f>IF(AC45=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC45" s="7">
+      <c r="BC45" s="5">
         <f>IF(AD45=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD45" s="7">
+      <c r="BD45" s="5">
         <f>IF(AE45=AE$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE45" s="7">
+      <c r="BE45" s="5">
         <f>IF(AF45=AF$47,1,0)</f>
         <v>1</v>
       </c>
@@ -12337,103 +12699,103 @@
       <c r="AF46" s="3">
         <v>64</v>
       </c>
-      <c r="AG46" s="7">
+      <c r="AG46" s="5">
         <f>IF(H46=H$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AH46" s="7">
+      <c r="AH46" s="5">
         <f>IF(I46=I$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI46" s="7">
+      <c r="AI46" s="5">
         <f>IF(J46=J$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ46" s="7">
+      <c r="AJ46" s="5">
         <f>IF(K46=K$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK46" s="7">
+      <c r="AK46" s="5">
         <f>IF(L46=L$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL46" s="7">
+      <c r="AL46" s="5">
         <f>IF(M46=M$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM46" s="7">
+      <c r="AM46" s="5">
         <f>IF(N46=N$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN46" s="7">
+      <c r="AN46" s="5">
         <f>IF(O46=O$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO46" s="7">
+      <c r="AO46" s="5">
         <f>IF(P46=P$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP46" s="7">
+      <c r="AP46" s="5">
         <f>IF(Q46=Q$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ46" s="7">
+      <c r="AQ46" s="5">
         <f>IF(R46=R$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR46" s="7">
+      <c r="AR46" s="5">
         <f>IF(S46=S$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS46" s="7">
+      <c r="AS46" s="5">
         <f>IF(T46=T$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT46" s="7">
+      <c r="AT46" s="5">
         <f>IF(U46=U$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU46" s="7">
+      <c r="AU46" s="5">
         <f>IF(V46=V$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV46" s="7">
+      <c r="AV46" s="5">
         <f>IF(W46=W$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW46" s="7">
+      <c r="AW46" s="5">
         <f>IF(X46=X$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX46" s="7">
+      <c r="AX46" s="5">
         <f>IF(Y46=Y$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY46" s="7">
+      <c r="AY46" s="5">
         <f>IF(Z46=Z$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ46" s="7">
+      <c r="AZ46" s="5">
         <f>IF(AA46=AA$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA46" s="7">
+      <c r="BA46" s="5">
         <f>IF(AB46=AB$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BB46" s="7">
+      <c r="BB46" s="5">
         <f>IF(AC46=AC$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC46" s="7">
+      <c r="BC46" s="5">
         <f>IF(AD46=AD$47,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD46" s="7">
+      <c r="BD46" s="5">
         <f>IF(AE46=AE$47,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BE46" s="7">
+      <c r="BE46" s="5">
         <f>IF(AF46=AF$47,1,0)</f>
         <v>0</v>
       </c>
@@ -12442,85 +12804,126 @@
         <v>80</v>
       </c>
     </row>
-    <row r="47" ht="22.5" customHeight="1" spans="8:33">
-      <c r="H47" s="5" t="s">
+    <row r="47" ht="22.5" customHeight="1" spans="1:58">
+      <c r="H47" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="I47" s="5" t="s">
+      <c r="I47" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="J47" s="5" t="s">
+      <c r="J47" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="K47" s="5" t="s">
+      <c r="K47" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="L47" s="5" t="s">
+      <c r="L47" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="M47" s="5" t="s">
+      <c r="M47" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="N47" s="5" t="s">
+      <c r="N47" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="O47" s="5" t="s">
+      <c r="O47" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="P47" s="5" t="s">
+      <c r="P47" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="Q47" s="5" t="s">
+      <c r="Q47" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="R47" s="5" t="s">
+      <c r="R47" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="S47" s="5" t="s">
+      <c r="S47" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="T47" s="6" t="s">
+      <c r="T47" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="U47" s="6" t="s">
+      <c r="U47" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="V47" s="6" t="s">
+      <c r="V47" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="W47" s="6" t="s">
+      <c r="W47" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="X47" s="6" t="s">
+      <c r="X47" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="Y47" s="6" t="s">
+      <c r="Y47" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="Z47" s="6" t="s">
+      <c r="Z47" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="AA47" s="6" t="s">
+      <c r="AA47" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="AB47" s="5">
+      <c r="AB47" s="6">
         <v>5</v>
       </c>
-      <c r="AC47" s="5">
+      <c r="AC47" s="6">
         <v>18</v>
       </c>
-      <c r="AD47" s="5">
+      <c r="AD47" s="6">
         <v>26</v>
       </c>
-      <c r="AE47" s="5">
-        <v>1</v>
-      </c>
-      <c r="AF47" s="5">
+      <c r="AE47" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF47" s="6">
         <v>3</v>
       </c>
-      <c r="AG47" s="7"/>
+      <c r="AG47" s="5"/>
     </row>
-    <row r="48" ht="22.5" customHeight="1"/>
+    <row r="48" ht="22.5" customHeight="1" spans="1:58">
+      <c r="A48" s="8"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="8"/>
+      <c r="M48" s="8"/>
+      <c r="N48" s="8"/>
+      <c r="O48" s="8"/>
+      <c r="P48" s="8"/>
+      <c r="Q48" s="8"/>
+      <c r="R48" s="8"/>
+      <c r="S48" s="8"/>
+      <c r="T48" s="8"/>
+      <c r="U48" s="8"/>
+      <c r="V48" s="8"/>
+      <c r="W48" s="8"/>
+      <c r="X48" s="8"/>
+      <c r="Y48" s="8"/>
+      <c r="Z48" s="8"/>
+      <c r="AA48" s="8"/>
+      <c r="AB48" s="8"/>
+      <c r="AC48" s="8"/>
+      <c r="AD48" s="8"/>
+      <c r="AE48" s="8"/>
+      <c r="AF48" s="8"/>
+      <c r="AG48" s="5">
+        <f>IF(H48=H$47,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF48">
+        <f>AVERAGE(BF2:BF46)</f>
+        <v>84.8</v>
+      </c>
+    </row>
     <row r="49" ht="22.5" customHeight="1"/>
     <row r="50" ht="22.5" customHeight="1"/>
     <row r="51" ht="22.5" customHeight="1"/>
